--- a/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
+++ b/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
@@ -317,7 +317,7 @@
     <t xml:space="preserve">ts_u16</t>
   </si>
   <si>
-    <t xml:space="preserve">PRESENT</t>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">=INTERPOLATE(ts_u3; 0; ts_u11; 70; 90; 73; 81)</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">ts_u17</t>
   </si>
   <si>
-    <t xml:space="preserve">CLOSED</t>
+    <t xml:space="preserve">0</t>
   </si>
   <si>
     <t xml:space="preserve">=ADD(ts_u3;12)</t>

--- a/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
+++ b/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="121">
   <si>
     <t xml:space="preserve">Dummy Test</t>
   </si>
@@ -518,9 +518,6 @@
     <t xml:space="preserve">ts_y21</t>
   </si>
   <si>
-    <t xml:space="preserve">ts_y22</t>
-  </si>
-  <si>
     <t xml:space="preserve">ts_y23</t>
   </si>
   <si>
@@ -531,12 +528,6 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ts_y25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ts_y26</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1064,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BZ64"/>
+  <dimension ref="A1:BZ1048576"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="64.17"/>
@@ -6031,22 +6022,22 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="32" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="39" t="n">
+      <c r="C60" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="34" t="s">
         <v>94</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F60" s="35" t="s">
-        <v>70</v>
+        <v>118</v>
+      </c>
+      <c r="F60" s="35" t="n">
+        <v>55</v>
       </c>
       <c r="G60" s="36"/>
       <c r="H60" s="36"/>
@@ -6123,10 +6114,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" s="33" t="n">
         <v>0</v>
@@ -6135,7 +6126,7 @@
         <v>94</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F61" s="35" t="n">
         <v>55</v>
@@ -6213,212 +6204,11 @@
       <c r="BY61" s="36"/>
       <c r="BZ61" s="36"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="C62" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E62" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="F62" s="35" t="n">
-        <v>55</v>
-      </c>
-      <c r="G62" s="36"/>
-      <c r="H62" s="36"/>
-      <c r="I62" s="36"/>
-      <c r="J62" s="36"/>
-      <c r="K62" s="36"/>
-      <c r="L62" s="36"/>
-      <c r="M62" s="36"/>
-      <c r="N62" s="36"/>
-      <c r="O62" s="36"/>
-      <c r="P62" s="36"/>
-      <c r="Q62" s="36"/>
-      <c r="R62" s="36"/>
-      <c r="S62" s="36"/>
-      <c r="T62" s="36"/>
-      <c r="U62" s="37"/>
-      <c r="V62" s="36"/>
-      <c r="W62" s="36"/>
-      <c r="X62" s="36"/>
-      <c r="Y62" s="36"/>
-      <c r="Z62" s="36"/>
-      <c r="AA62" s="36"/>
-      <c r="AB62" s="36"/>
-      <c r="AC62" s="36"/>
-      <c r="AD62" s="36"/>
-      <c r="AE62" s="36"/>
-      <c r="AF62" s="36"/>
-      <c r="AG62" s="36"/>
-      <c r="AH62" s="36"/>
-      <c r="AI62" s="36"/>
-      <c r="AJ62" s="36"/>
-      <c r="AK62" s="36"/>
-      <c r="AL62" s="36"/>
-      <c r="AM62" s="37"/>
-      <c r="AN62" s="36"/>
-      <c r="AO62" s="36"/>
-      <c r="AP62" s="36"/>
-      <c r="AQ62" s="36"/>
-      <c r="AR62" s="36"/>
-      <c r="AS62" s="36"/>
-      <c r="AT62" s="36"/>
-      <c r="AU62" s="36"/>
-      <c r="AV62" s="36"/>
-      <c r="AW62" s="37"/>
-      <c r="AX62" s="36"/>
-      <c r="AY62" s="36"/>
-      <c r="AZ62" s="36"/>
-      <c r="BA62" s="36"/>
-      <c r="BB62" s="36"/>
-      <c r="BC62" s="36"/>
-      <c r="BD62" s="36"/>
-      <c r="BE62" s="36"/>
-      <c r="BF62" s="36"/>
-      <c r="BG62" s="36"/>
-      <c r="BH62" s="36"/>
-      <c r="BI62" s="36"/>
-      <c r="BJ62" s="36"/>
-      <c r="BK62" s="36"/>
-      <c r="BL62" s="36"/>
-      <c r="BM62" s="36"/>
-      <c r="BN62" s="36"/>
-      <c r="BO62" s="36"/>
-      <c r="BP62" s="37"/>
-      <c r="BQ62" s="38"/>
-      <c r="BR62" s="36"/>
-      <c r="BS62" s="36"/>
-      <c r="BT62" s="36"/>
-      <c r="BU62" s="36"/>
-      <c r="BV62" s="36"/>
-      <c r="BW62" s="36"/>
-      <c r="BX62" s="36"/>
-      <c r="BY62" s="36"/>
-      <c r="BZ62" s="36"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B63" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C63" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="G63" s="36"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="36"/>
-      <c r="J63" s="36"/>
-      <c r="K63" s="36"/>
-      <c r="L63" s="36"/>
-      <c r="M63" s="36"/>
-      <c r="N63" s="36"/>
-      <c r="O63" s="36"/>
-      <c r="P63" s="36"/>
-      <c r="Q63" s="36"/>
-      <c r="R63" s="36"/>
-      <c r="S63" s="36"/>
-      <c r="T63" s="36"/>
-      <c r="U63" s="37"/>
-      <c r="V63" s="36"/>
-      <c r="W63" s="36"/>
-      <c r="X63" s="36"/>
-      <c r="Y63" s="36"/>
-      <c r="Z63" s="36"/>
-      <c r="AA63" s="36"/>
-      <c r="AB63" s="36"/>
-      <c r="AC63" s="36"/>
-      <c r="AD63" s="36"/>
-      <c r="AE63" s="36"/>
-      <c r="AF63" s="36"/>
-      <c r="AG63" s="36"/>
-      <c r="AH63" s="36"/>
-      <c r="AI63" s="36"/>
-      <c r="AJ63" s="36"/>
-      <c r="AK63" s="36"/>
-      <c r="AL63" s="36"/>
-      <c r="AM63" s="37"/>
-      <c r="AN63" s="36"/>
-      <c r="AO63" s="36"/>
-      <c r="AP63" s="36"/>
-      <c r="AQ63" s="36"/>
-      <c r="AR63" s="36"/>
-      <c r="AS63" s="36"/>
-      <c r="AT63" s="36"/>
-      <c r="AU63" s="36"/>
-      <c r="AV63" s="36"/>
-      <c r="AW63" s="37"/>
-      <c r="AX63" s="36"/>
-      <c r="AY63" s="36"/>
-      <c r="AZ63" s="36"/>
-      <c r="BA63" s="36"/>
-      <c r="BB63" s="36"/>
-      <c r="BC63" s="36"/>
-      <c r="BD63" s="36"/>
-      <c r="BE63" s="36"/>
-      <c r="BF63" s="36"/>
-      <c r="BG63" s="36"/>
-      <c r="BH63" s="36"/>
-      <c r="BI63" s="36"/>
-      <c r="BJ63" s="36"/>
-      <c r="BK63" s="36"/>
-      <c r="BL63" s="36"/>
-      <c r="BM63" s="36"/>
-      <c r="BN63" s="36"/>
-      <c r="BO63" s="36"/>
-      <c r="BP63" s="37"/>
-      <c r="BQ63" s="38"/>
-      <c r="BR63" s="36"/>
-      <c r="BS63" s="36"/>
-      <c r="BT63" s="36"/>
-      <c r="BU63" s="36"/>
-      <c r="BV63" s="36"/>
-      <c r="BW63" s="36"/>
-      <c r="BX63" s="36"/>
-      <c r="BY63" s="36"/>
-      <c r="BZ63" s="36"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="B64" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E64" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="35" t="s">
-        <v>80</v>
-      </c>
-    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="G8:ZY33 G39:ZY63">
+  <conditionalFormatting sqref="G8:ZY33 G39:ZY61">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>#ref!&lt;&gt;G8</formula>
     </cfRule>

--- a/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
+++ b/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
@@ -25,7 +25,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="S5" authorId="0">
+    <comment ref="T5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -40,7 +40,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0">
+    <comment ref="U5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,21 +52,6 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     "0 total cooling requests remains at time data are recorded since loop output is &lt;85%" wording is unclear</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AH35" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Needs to be increased.  Airflow needs to be &lt;70% of setpoint for 10 mins</t>
         </r>
       </text>
     </comment>
@@ -85,7 +70,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL35" authorId="0">
+    <comment ref="AJ35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Needs to be increased.  Airflow needs to be &lt;70% of setpoint for 10 mins</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AV37" authorId="0">
+    <comment ref="AW37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BB50" authorId="0">
+    <comment ref="BC50" authorId="0">
       <text>
         <r>
           <rPr>
@@ -141,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BC37" authorId="0">
+    <comment ref="BD37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="128">
   <si>
     <t xml:space="preserve">Dummy Test</t>
   </si>
@@ -191,6 +191,18 @@
     <t xml:space="preserve">Test Step</t>
   </si>
   <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -275,6 +287,9 @@
     <t xml:space="preserve">=RAMP(68; 72; 60; 10)</t>
   </si>
   <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
     <t xml:space="preserve">L</t>
   </si>
   <si>
@@ -431,12 +446,24 @@
     <t xml:space="preserve">VariableName</t>
   </si>
   <si>
+    <t xml:space="preserve">ts_y1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Variable Value</t>
   </si>
   <si>
     <t xml:space="preserve">VariableValue</t>
   </si>
   <si>
+    <t xml:space="preserve">&gt;=69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;=71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ts_y11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Expected Outputs</t>
   </si>
   <si>
@@ -446,9 +473,6 @@
     <t xml:space="preserve">OutputTolerance</t>
   </si>
   <si>
-    <t xml:space="preserve">ts_y1</t>
-  </si>
-  <si>
     <t xml:space="preserve">=ANY</t>
   </si>
   <si>
@@ -477,9 +501,6 @@
   </si>
   <si>
     <t xml:space="preserve">ts_y10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ts_y11</t>
   </si>
   <si>
     <t xml:space="preserve">ts_y12</t>
@@ -1064,18 +1085,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BZ1048576"/>
+  <dimension ref="A1:CA61"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="64.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="2" width="50.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="78" min="7" style="3" width="50.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="79" style="3" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="7" style="3" width="50.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="80" style="3" width="8.83"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="7" customFormat="true" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1092,16 +1113,16 @@
       <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="U1" s="8"/>
-      <c r="V1" s="9"/>
-      <c r="AM1" s="8"/>
-      <c r="AN1" s="9"/>
-      <c r="AW1" s="8"/>
-      <c r="AX1" s="9"/>
-      <c r="BP1" s="8"/>
-      <c r="BQ1" s="9"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="9"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="9"/>
+      <c r="AX1" s="8"/>
+      <c r="AY1" s="9"/>
+      <c r="BQ1" s="8"/>
+      <c r="BR1" s="9"/>
     </row>
-    <row r="2" s="10" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="10" customFormat="true" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1118,16 +1139,16 @@
       <c r="F2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="U2" s="11"/>
-      <c r="V2" s="12"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="12"/>
-      <c r="AW2" s="11"/>
-      <c r="AX2" s="12"/>
-      <c r="BP2" s="11"/>
-      <c r="BQ2" s="12"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="12"/>
+      <c r="AN2" s="11"/>
+      <c r="AO2" s="12"/>
+      <c r="AX2" s="11"/>
+      <c r="AY2" s="12"/>
+      <c r="BQ2" s="11"/>
+      <c r="BR2" s="12"/>
     </row>
-    <row r="3" s="10" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" s="10" customFormat="true" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1158,9 +1179,9 @@
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="14"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
@@ -1176,9 +1197,9 @@
       <c r="AJ3" s="5"/>
       <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
-      <c r="AM3" s="13"/>
-      <c r="AN3" s="14"/>
-      <c r="AO3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="13"/>
+      <c r="AO3" s="14"/>
       <c r="AP3" s="5"/>
       <c r="AQ3" s="5"/>
       <c r="AR3" s="5"/>
@@ -1186,9 +1207,9 @@
       <c r="AT3" s="5"/>
       <c r="AU3" s="5"/>
       <c r="AV3" s="5"/>
-      <c r="AW3" s="13"/>
-      <c r="AX3" s="14"/>
-      <c r="AY3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="13"/>
+      <c r="AY3" s="14"/>
       <c r="AZ3" s="5"/>
       <c r="BA3" s="5"/>
       <c r="BB3" s="5"/>
@@ -1205,9 +1226,9 @@
       <c r="BM3" s="5"/>
       <c r="BN3" s="5"/>
       <c r="BO3" s="5"/>
-      <c r="BP3" s="13"/>
-      <c r="BQ3" s="14"/>
-      <c r="BR3" s="5"/>
+      <c r="BP3" s="5"/>
+      <c r="BQ3" s="13"/>
+      <c r="BR3" s="14"/>
       <c r="BS3" s="5"/>
       <c r="BT3" s="5"/>
       <c r="BU3" s="5"/>
@@ -1216,8 +1237,9 @@
       <c r="BX3" s="5"/>
       <c r="BY3" s="5"/>
       <c r="BZ3" s="5"/>
+      <c r="CA3" s="5"/>
     </row>
-    <row r="4" s="10" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="10" customFormat="true" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1231,16 +1253,16 @@
       <c r="F4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="U4" s="11"/>
-      <c r="V4" s="12"/>
-      <c r="AM4" s="11"/>
-      <c r="AN4" s="12"/>
-      <c r="AW4" s="11"/>
-      <c r="AX4" s="12"/>
-      <c r="BP4" s="11"/>
-      <c r="BQ4" s="12"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="12"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="12"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="12"/>
+      <c r="BQ4" s="11"/>
+      <c r="BR4" s="12"/>
     </row>
-    <row r="5" s="10" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" s="10" customFormat="true" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
@@ -1255,12 +1277,12 @@
       <c r="F5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="U5" s="11"/>
-      <c r="V5" s="12"/>
-      <c r="AM5" s="11"/>
-      <c r="AW5" s="11"/>
-      <c r="BP5" s="11"/>
-      <c r="BQ5" s="12"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="12"/>
+      <c r="AN5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="BQ5" s="11"/>
+      <c r="BR5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
@@ -1281,10 +1303,18 @@
       <c r="F6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+      <c r="G6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>4</v>
+      </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
@@ -1295,9 +1325,9 @@
       <c r="R6" s="19"/>
       <c r="S6" s="19"/>
       <c r="T6" s="19"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="22"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="21"/>
       <c r="X6" s="22"/>
       <c r="Y6" s="22"/>
       <c r="Z6" s="22"/>
@@ -1313,9 +1343,9 @@
       <c r="AJ6" s="22"/>
       <c r="AK6" s="22"/>
       <c r="AL6" s="22"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="24"/>
-      <c r="AO6" s="19"/>
+      <c r="AM6" s="22"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="24"/>
       <c r="AP6" s="19"/>
       <c r="AQ6" s="19"/>
       <c r="AR6" s="19"/>
@@ -1323,9 +1353,9 @@
       <c r="AT6" s="19"/>
       <c r="AU6" s="19"/>
       <c r="AV6" s="19"/>
-      <c r="AW6" s="20"/>
-      <c r="AX6" s="21"/>
-      <c r="AY6" s="22"/>
+      <c r="AW6" s="19"/>
+      <c r="AX6" s="20"/>
+      <c r="AY6" s="21"/>
       <c r="AZ6" s="22"/>
       <c r="BA6" s="22"/>
       <c r="BB6" s="22"/>
@@ -1342,9 +1372,9 @@
       <c r="BM6" s="22"/>
       <c r="BN6" s="22"/>
       <c r="BO6" s="22"/>
-      <c r="BP6" s="23"/>
-      <c r="BQ6" s="24"/>
-      <c r="BR6" s="19"/>
+      <c r="BP6" s="22"/>
+      <c r="BQ6" s="23"/>
+      <c r="BR6" s="24"/>
       <c r="BS6" s="19"/>
       <c r="BT6" s="19"/>
       <c r="BU6" s="19"/>
@@ -1353,6 +1383,7 @@
       <c r="BX6" s="19"/>
       <c r="BY6" s="19"/>
       <c r="BZ6" s="19"/>
+      <c r="CA6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
@@ -1375,10 +1406,18 @@
       <c r="F7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
+      <c r="G7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>11</v>
+      </c>
       <c r="K7" s="26"/>
       <c r="L7" s="26"/>
       <c r="M7" s="26"/>
@@ -1389,9 +1428,9 @@
       <c r="R7" s="26"/>
       <c r="S7" s="26"/>
       <c r="T7" s="26"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="29"/>
+      <c r="U7" s="26"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="28"/>
       <c r="X7" s="29"/>
       <c r="Y7" s="29"/>
       <c r="Z7" s="29"/>
@@ -1407,9 +1446,9 @@
       <c r="AJ7" s="29"/>
       <c r="AK7" s="29"/>
       <c r="AL7" s="29"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="31"/>
-      <c r="AO7" s="26"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="31"/>
       <c r="AP7" s="26"/>
       <c r="AQ7" s="26"/>
       <c r="AR7" s="26"/>
@@ -1417,9 +1456,9 @@
       <c r="AT7" s="26"/>
       <c r="AU7" s="26"/>
       <c r="AV7" s="26"/>
-      <c r="AW7" s="27"/>
-      <c r="AX7" s="28"/>
-      <c r="AY7" s="29"/>
+      <c r="AW7" s="26"/>
+      <c r="AX7" s="27"/>
+      <c r="AY7" s="28"/>
       <c r="AZ7" s="29"/>
       <c r="BA7" s="29"/>
       <c r="BB7" s="29"/>
@@ -1436,9 +1475,9 @@
       <c r="BM7" s="29"/>
       <c r="BN7" s="29"/>
       <c r="BO7" s="29"/>
-      <c r="BP7" s="30"/>
-      <c r="BQ7" s="31"/>
-      <c r="BR7" s="26"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="31"/>
       <c r="BS7" s="26"/>
       <c r="BT7" s="26"/>
       <c r="BU7" s="26"/>
@@ -1447,13 +1486,14 @@
       <c r="BX7" s="26"/>
       <c r="BY7" s="26"/>
       <c r="BZ7" s="26"/>
+      <c r="CA7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="34" t="n">
@@ -1465,10 +1505,18 @@
       <c r="F8" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
+      <c r="G8" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="K8" s="36"/>
       <c r="L8" s="36"/>
       <c r="M8" s="36"/>
@@ -1479,9 +1527,9 @@
       <c r="R8" s="36"/>
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="38"/>
       <c r="X8" s="36"/>
       <c r="Y8" s="36"/>
       <c r="Z8" s="36"/>
@@ -1497,9 +1545,9 @@
       <c r="AJ8" s="36"/>
       <c r="AK8" s="36"/>
       <c r="AL8" s="36"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="38"/>
-      <c r="AO8" s="36"/>
+      <c r="AM8" s="36"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="38"/>
       <c r="AP8" s="36"/>
       <c r="AQ8" s="36"/>
       <c r="AR8" s="36"/>
@@ -1507,9 +1555,9 @@
       <c r="AT8" s="36"/>
       <c r="AU8" s="36"/>
       <c r="AV8" s="36"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="38"/>
-      <c r="AY8" s="36"/>
+      <c r="AW8" s="36"/>
+      <c r="AX8" s="37"/>
+      <c r="AY8" s="38"/>
       <c r="AZ8" s="36"/>
       <c r="BA8" s="36"/>
       <c r="BB8" s="36"/>
@@ -1526,9 +1574,9 @@
       <c r="BM8" s="36"/>
       <c r="BN8" s="36"/>
       <c r="BO8" s="36"/>
-      <c r="BP8" s="37"/>
-      <c r="BQ8" s="38"/>
-      <c r="BR8" s="36"/>
+      <c r="BP8" s="36"/>
+      <c r="BQ8" s="37"/>
+      <c r="BR8" s="38"/>
       <c r="BS8" s="36"/>
       <c r="BT8" s="36"/>
       <c r="BU8" s="36"/>
@@ -1537,13 +1585,14 @@
       <c r="BX8" s="36"/>
       <c r="BY8" s="36"/>
       <c r="BZ8" s="36"/>
+      <c r="CA8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="35" t="n">
@@ -1555,10 +1604,18 @@
       <c r="F9" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
+      <c r="G9" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>75</v>
+      </c>
       <c r="K9" s="36"/>
       <c r="L9" s="36"/>
       <c r="M9" s="36"/>
@@ -1569,9 +1626,9 @@
       <c r="R9" s="36"/>
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="38"/>
       <c r="X9" s="36"/>
       <c r="Y9" s="36"/>
       <c r="Z9" s="36"/>
@@ -1587,9 +1644,9 @@
       <c r="AJ9" s="36"/>
       <c r="AK9" s="36"/>
       <c r="AL9" s="36"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="38"/>
-      <c r="AO9" s="36"/>
+      <c r="AM9" s="36"/>
+      <c r="AN9" s="37"/>
+      <c r="AO9" s="38"/>
       <c r="AP9" s="36"/>
       <c r="AQ9" s="36"/>
       <c r="AR9" s="36"/>
@@ -1597,9 +1654,9 @@
       <c r="AT9" s="36"/>
       <c r="AU9" s="36"/>
       <c r="AV9" s="36"/>
-      <c r="AW9" s="37"/>
-      <c r="AX9" s="38"/>
-      <c r="AY9" s="36"/>
+      <c r="AW9" s="36"/>
+      <c r="AX9" s="37"/>
+      <c r="AY9" s="38"/>
       <c r="AZ9" s="36"/>
       <c r="BA9" s="36"/>
       <c r="BB9" s="36"/>
@@ -1616,9 +1673,9 @@
       <c r="BM9" s="36"/>
       <c r="BN9" s="36"/>
       <c r="BO9" s="36"/>
-      <c r="BP9" s="37"/>
-      <c r="BQ9" s="38"/>
-      <c r="BR9" s="36"/>
+      <c r="BP9" s="36"/>
+      <c r="BQ9" s="37"/>
+      <c r="BR9" s="38"/>
       <c r="BS9" s="36"/>
       <c r="BT9" s="36"/>
       <c r="BU9" s="36"/>
@@ -1627,13 +1684,14 @@
       <c r="BX9" s="36"/>
       <c r="BY9" s="36"/>
       <c r="BZ9" s="36"/>
+      <c r="CA9" s="36"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10" s="39"/>
       <c r="D10" s="35" t="n">
@@ -1645,10 +1703,18 @@
       <c r="F10" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
+      <c r="G10" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" s="35" t="n">
+        <v>60</v>
+      </c>
       <c r="K10" s="36"/>
       <c r="L10" s="36"/>
       <c r="M10" s="36"/>
@@ -1659,9 +1725,9 @@
       <c r="R10" s="36"/>
       <c r="S10" s="36"/>
       <c r="T10" s="36"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="38"/>
       <c r="X10" s="36"/>
       <c r="Y10" s="36"/>
       <c r="Z10" s="36"/>
@@ -1677,9 +1743,9 @@
       <c r="AJ10" s="36"/>
       <c r="AK10" s="36"/>
       <c r="AL10" s="36"/>
-      <c r="AM10" s="37"/>
-      <c r="AN10" s="38"/>
-      <c r="AO10" s="36"/>
+      <c r="AM10" s="36"/>
+      <c r="AN10" s="37"/>
+      <c r="AO10" s="38"/>
       <c r="AP10" s="36"/>
       <c r="AQ10" s="36"/>
       <c r="AR10" s="36"/>
@@ -1687,9 +1753,9 @@
       <c r="AT10" s="36"/>
       <c r="AU10" s="36"/>
       <c r="AV10" s="36"/>
-      <c r="AW10" s="37"/>
-      <c r="AX10" s="38"/>
-      <c r="AY10" s="36"/>
+      <c r="AW10" s="36"/>
+      <c r="AX10" s="37"/>
+      <c r="AY10" s="38"/>
       <c r="AZ10" s="36"/>
       <c r="BA10" s="36"/>
       <c r="BB10" s="36"/>
@@ -1706,9 +1772,9 @@
       <c r="BM10" s="36"/>
       <c r="BN10" s="36"/>
       <c r="BO10" s="36"/>
-      <c r="BP10" s="37"/>
-      <c r="BQ10" s="38"/>
-      <c r="BR10" s="36"/>
+      <c r="BP10" s="36"/>
+      <c r="BQ10" s="37"/>
+      <c r="BR10" s="38"/>
       <c r="BS10" s="36"/>
       <c r="BT10" s="36"/>
       <c r="BU10" s="36"/>
@@ -1717,13 +1783,14 @@
       <c r="BX10" s="36"/>
       <c r="BY10" s="36"/>
       <c r="BZ10" s="36"/>
+      <c r="CA10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C11" s="39"/>
       <c r="D11" s="35" t="n">
@@ -1735,10 +1802,18 @@
       <c r="F11" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
+      <c r="G11" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="J11" s="35" t="n">
+        <v>90</v>
+      </c>
       <c r="K11" s="36"/>
       <c r="L11" s="36"/>
       <c r="M11" s="36"/>
@@ -1749,9 +1824,9 @@
       <c r="R11" s="36"/>
       <c r="S11" s="36"/>
       <c r="T11" s="36"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="38"/>
       <c r="X11" s="36"/>
       <c r="Y11" s="36"/>
       <c r="Z11" s="36"/>
@@ -1767,9 +1842,9 @@
       <c r="AJ11" s="36"/>
       <c r="AK11" s="36"/>
       <c r="AL11" s="36"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="38"/>
-      <c r="AO11" s="36"/>
+      <c r="AM11" s="36"/>
+      <c r="AN11" s="37"/>
+      <c r="AO11" s="38"/>
       <c r="AP11" s="36"/>
       <c r="AQ11" s="36"/>
       <c r="AR11" s="36"/>
@@ -1777,9 +1852,9 @@
       <c r="AT11" s="36"/>
       <c r="AU11" s="36"/>
       <c r="AV11" s="36"/>
-      <c r="AW11" s="37"/>
-      <c r="AX11" s="38"/>
-      <c r="AY11" s="36"/>
+      <c r="AW11" s="36"/>
+      <c r="AX11" s="37"/>
+      <c r="AY11" s="38"/>
       <c r="AZ11" s="36"/>
       <c r="BA11" s="36"/>
       <c r="BB11" s="36"/>
@@ -1796,9 +1871,9 @@
       <c r="BM11" s="36"/>
       <c r="BN11" s="36"/>
       <c r="BO11" s="36"/>
-      <c r="BP11" s="37"/>
-      <c r="BQ11" s="38"/>
-      <c r="BR11" s="36"/>
+      <c r="BP11" s="36"/>
+      <c r="BQ11" s="37"/>
+      <c r="BR11" s="38"/>
       <c r="BS11" s="36"/>
       <c r="BT11" s="36"/>
       <c r="BU11" s="36"/>
@@ -1807,13 +1882,14 @@
       <c r="BX11" s="36"/>
       <c r="BY11" s="36"/>
       <c r="BZ11" s="36"/>
+      <c r="CA11" s="36"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C12" s="33"/>
       <c r="D12" s="35" t="n">
@@ -1825,10 +1901,18 @@
       <c r="F12" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
+      <c r="G12" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="K12" s="36"/>
       <c r="L12" s="36"/>
       <c r="M12" s="36"/>
@@ -1839,9 +1923,9 @@
       <c r="R12" s="36"/>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="38"/>
       <c r="X12" s="36"/>
       <c r="Y12" s="36"/>
       <c r="Z12" s="36"/>
@@ -1857,9 +1941,9 @@
       <c r="AJ12" s="36"/>
       <c r="AK12" s="36"/>
       <c r="AL12" s="36"/>
-      <c r="AM12" s="37"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="36"/>
+      <c r="AM12" s="36"/>
+      <c r="AN12" s="37"/>
+      <c r="AO12" s="38"/>
       <c r="AP12" s="36"/>
       <c r="AQ12" s="36"/>
       <c r="AR12" s="36"/>
@@ -1867,9 +1951,9 @@
       <c r="AT12" s="36"/>
       <c r="AU12" s="36"/>
       <c r="AV12" s="36"/>
-      <c r="AW12" s="37"/>
-      <c r="AX12" s="38"/>
-      <c r="AY12" s="36"/>
+      <c r="AW12" s="36"/>
+      <c r="AX12" s="37"/>
+      <c r="AY12" s="38"/>
       <c r="AZ12" s="36"/>
       <c r="BA12" s="36"/>
       <c r="BB12" s="36"/>
@@ -1886,9 +1970,9 @@
       <c r="BM12" s="36"/>
       <c r="BN12" s="36"/>
       <c r="BO12" s="36"/>
-      <c r="BP12" s="37"/>
-      <c r="BQ12" s="38"/>
-      <c r="BR12" s="36"/>
+      <c r="BP12" s="36"/>
+      <c r="BQ12" s="37"/>
+      <c r="BR12" s="38"/>
       <c r="BS12" s="36"/>
       <c r="BT12" s="36"/>
       <c r="BU12" s="36"/>
@@ -1897,28 +1981,37 @@
       <c r="BX12" s="36"/>
       <c r="BY12" s="36"/>
       <c r="BZ12" s="36"/>
+      <c r="CA12" s="36"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="35" t="n">
         <v>500</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F13" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
+      <c r="G13" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="J13" s="35" t="n">
+        <v>500</v>
+      </c>
       <c r="K13" s="36"/>
       <c r="L13" s="36"/>
       <c r="M13" s="36"/>
@@ -1929,9 +2022,9 @@
       <c r="R13" s="36"/>
       <c r="S13" s="36"/>
       <c r="T13" s="36"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="38"/>
       <c r="X13" s="36"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="36"/>
@@ -1947,9 +2040,9 @@
       <c r="AJ13" s="36"/>
       <c r="AK13" s="36"/>
       <c r="AL13" s="36"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="38"/>
-      <c r="AO13" s="36"/>
+      <c r="AM13" s="36"/>
+      <c r="AN13" s="37"/>
+      <c r="AO13" s="38"/>
       <c r="AP13" s="36"/>
       <c r="AQ13" s="36"/>
       <c r="AR13" s="36"/>
@@ -1957,9 +2050,9 @@
       <c r="AT13" s="36"/>
       <c r="AU13" s="36"/>
       <c r="AV13" s="36"/>
-      <c r="AW13" s="37"/>
-      <c r="AX13" s="38"/>
-      <c r="AY13" s="36"/>
+      <c r="AW13" s="36"/>
+      <c r="AX13" s="37"/>
+      <c r="AY13" s="38"/>
       <c r="AZ13" s="36"/>
       <c r="BA13" s="36"/>
       <c r="BB13" s="36"/>
@@ -1976,9 +2069,9 @@
       <c r="BM13" s="36"/>
       <c r="BN13" s="36"/>
       <c r="BO13" s="36"/>
-      <c r="BP13" s="37"/>
-      <c r="BQ13" s="38"/>
-      <c r="BR13" s="36"/>
+      <c r="BP13" s="36"/>
+      <c r="BQ13" s="37"/>
+      <c r="BR13" s="38"/>
       <c r="BS13" s="36"/>
       <c r="BT13" s="36"/>
       <c r="BU13" s="36"/>
@@ -1987,13 +2080,14 @@
       <c r="BX13" s="36"/>
       <c r="BY13" s="36"/>
       <c r="BZ13" s="36"/>
+      <c r="CA13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="35" t="n">
@@ -2005,10 +2099,18 @@
       <c r="F14" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
+      <c r="G14" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" s="35" t="n">
+        <v>100</v>
+      </c>
       <c r="K14" s="36"/>
       <c r="L14" s="36"/>
       <c r="M14" s="36"/>
@@ -2019,9 +2121,9 @@
       <c r="R14" s="36"/>
       <c r="S14" s="36"/>
       <c r="T14" s="36"/>
-      <c r="U14" s="37"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="38"/>
       <c r="X14" s="36"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="36"/>
@@ -2037,9 +2139,9 @@
       <c r="AJ14" s="36"/>
       <c r="AK14" s="36"/>
       <c r="AL14" s="36"/>
-      <c r="AM14" s="37"/>
-      <c r="AN14" s="38"/>
-      <c r="AO14" s="36"/>
+      <c r="AM14" s="36"/>
+      <c r="AN14" s="37"/>
+      <c r="AO14" s="38"/>
       <c r="AP14" s="36"/>
       <c r="AQ14" s="36"/>
       <c r="AR14" s="36"/>
@@ -2047,9 +2149,9 @@
       <c r="AT14" s="36"/>
       <c r="AU14" s="36"/>
       <c r="AV14" s="36"/>
-      <c r="AW14" s="37"/>
-      <c r="AX14" s="38"/>
-      <c r="AY14" s="36"/>
+      <c r="AW14" s="36"/>
+      <c r="AX14" s="37"/>
+      <c r="AY14" s="38"/>
       <c r="AZ14" s="36"/>
       <c r="BA14" s="36"/>
       <c r="BB14" s="36"/>
@@ -2066,9 +2168,9 @@
       <c r="BM14" s="36"/>
       <c r="BN14" s="36"/>
       <c r="BO14" s="36"/>
-      <c r="BP14" s="37"/>
-      <c r="BQ14" s="38"/>
-      <c r="BR14" s="36"/>
+      <c r="BP14" s="36"/>
+      <c r="BQ14" s="37"/>
+      <c r="BR14" s="38"/>
       <c r="BS14" s="36"/>
       <c r="BT14" s="36"/>
       <c r="BU14" s="36"/>
@@ -2077,28 +2179,37 @@
       <c r="BX14" s="36"/>
       <c r="BY14" s="36"/>
       <c r="BZ14" s="36"/>
+      <c r="CA14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="35" t="n">
         <v>200</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F15" s="35" t="n">
         <v>200</v>
       </c>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
+      <c r="G15" s="35" t="n">
+        <v>200</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>200</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <v>200</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>200</v>
+      </c>
       <c r="K15" s="36"/>
       <c r="L15" s="36"/>
       <c r="M15" s="36"/>
@@ -2109,9 +2220,9 @@
       <c r="R15" s="36"/>
       <c r="S15" s="36"/>
       <c r="T15" s="36"/>
-      <c r="U15" s="37"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="37"/>
+      <c r="W15" s="38"/>
       <c r="X15" s="36"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="36"/>
@@ -2127,9 +2238,9 @@
       <c r="AJ15" s="36"/>
       <c r="AK15" s="36"/>
       <c r="AL15" s="36"/>
-      <c r="AM15" s="37"/>
-      <c r="AN15" s="38"/>
-      <c r="AO15" s="36"/>
+      <c r="AM15" s="36"/>
+      <c r="AN15" s="37"/>
+      <c r="AO15" s="38"/>
       <c r="AP15" s="36"/>
       <c r="AQ15" s="36"/>
       <c r="AR15" s="36"/>
@@ -2137,9 +2248,9 @@
       <c r="AT15" s="36"/>
       <c r="AU15" s="36"/>
       <c r="AV15" s="36"/>
-      <c r="AW15" s="37"/>
-      <c r="AX15" s="38"/>
-      <c r="AY15" s="36"/>
+      <c r="AW15" s="36"/>
+      <c r="AX15" s="37"/>
+      <c r="AY15" s="38"/>
       <c r="AZ15" s="36"/>
       <c r="BA15" s="36"/>
       <c r="BB15" s="36"/>
@@ -2156,9 +2267,9 @@
       <c r="BM15" s="36"/>
       <c r="BN15" s="36"/>
       <c r="BO15" s="36"/>
-      <c r="BP15" s="37"/>
-      <c r="BQ15" s="38"/>
-      <c r="BR15" s="36"/>
+      <c r="BP15" s="36"/>
+      <c r="BQ15" s="37"/>
+      <c r="BR15" s="38"/>
       <c r="BS15" s="36"/>
       <c r="BT15" s="36"/>
       <c r="BU15" s="36"/>
@@ -2167,28 +2278,37 @@
       <c r="BX15" s="36"/>
       <c r="BY15" s="36"/>
       <c r="BZ15" s="36"/>
+      <c r="CA15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="35" t="n">
         <v>120</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F16" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
+      <c r="G16" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="I16" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>120</v>
+      </c>
       <c r="K16" s="36"/>
       <c r="L16" s="36"/>
       <c r="M16" s="36"/>
@@ -2199,9 +2319,9 @@
       <c r="R16" s="36"/>
       <c r="S16" s="36"/>
       <c r="T16" s="36"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="36"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="37"/>
+      <c r="W16" s="38"/>
       <c r="X16" s="36"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="36"/>
@@ -2217,9 +2337,9 @@
       <c r="AJ16" s="36"/>
       <c r="AK16" s="36"/>
       <c r="AL16" s="36"/>
-      <c r="AM16" s="37"/>
-      <c r="AN16" s="38"/>
-      <c r="AO16" s="36"/>
+      <c r="AM16" s="36"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="38"/>
       <c r="AP16" s="36"/>
       <c r="AQ16" s="36"/>
       <c r="AR16" s="36"/>
@@ -2227,9 +2347,9 @@
       <c r="AT16" s="36"/>
       <c r="AU16" s="36"/>
       <c r="AV16" s="36"/>
-      <c r="AW16" s="37"/>
-      <c r="AX16" s="38"/>
-      <c r="AY16" s="36"/>
+      <c r="AW16" s="36"/>
+      <c r="AX16" s="37"/>
+      <c r="AY16" s="38"/>
       <c r="AZ16" s="36"/>
       <c r="BA16" s="36"/>
       <c r="BB16" s="36"/>
@@ -2246,9 +2366,9 @@
       <c r="BM16" s="36"/>
       <c r="BN16" s="36"/>
       <c r="BO16" s="36"/>
-      <c r="BP16" s="37"/>
-      <c r="BQ16" s="38"/>
-      <c r="BR16" s="36"/>
+      <c r="BP16" s="36"/>
+      <c r="BQ16" s="37"/>
+      <c r="BR16" s="38"/>
       <c r="BS16" s="36"/>
       <c r="BT16" s="36"/>
       <c r="BU16" s="36"/>
@@ -2257,28 +2377,37 @@
       <c r="BX16" s="36"/>
       <c r="BY16" s="36"/>
       <c r="BZ16" s="36"/>
+      <c r="CA16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="35" t="n">
         <v>20</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
+      <c r="G17" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>20</v>
+      </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
       <c r="M17" s="36"/>
@@ -2289,9 +2418,9 @@
       <c r="R17" s="36"/>
       <c r="S17" s="36"/>
       <c r="T17" s="36"/>
-      <c r="U17" s="37"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="36"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="38"/>
       <c r="X17" s="36"/>
       <c r="Y17" s="36"/>
       <c r="Z17" s="36"/>
@@ -2307,9 +2436,9 @@
       <c r="AJ17" s="36"/>
       <c r="AK17" s="36"/>
       <c r="AL17" s="36"/>
-      <c r="AM17" s="37"/>
-      <c r="AN17" s="38"/>
-      <c r="AO17" s="36"/>
+      <c r="AM17" s="36"/>
+      <c r="AN17" s="37"/>
+      <c r="AO17" s="38"/>
       <c r="AP17" s="36"/>
       <c r="AQ17" s="36"/>
       <c r="AR17" s="36"/>
@@ -2317,9 +2446,9 @@
       <c r="AT17" s="36"/>
       <c r="AU17" s="36"/>
       <c r="AV17" s="36"/>
-      <c r="AW17" s="37"/>
-      <c r="AX17" s="38"/>
-      <c r="AY17" s="36"/>
+      <c r="AW17" s="36"/>
+      <c r="AX17" s="37"/>
+      <c r="AY17" s="38"/>
       <c r="AZ17" s="36"/>
       <c r="BA17" s="36"/>
       <c r="BB17" s="36"/>
@@ -2336,9 +2465,9 @@
       <c r="BM17" s="36"/>
       <c r="BN17" s="36"/>
       <c r="BO17" s="36"/>
-      <c r="BP17" s="37"/>
-      <c r="BQ17" s="38"/>
-      <c r="BR17" s="36"/>
+      <c r="BP17" s="36"/>
+      <c r="BQ17" s="37"/>
+      <c r="BR17" s="38"/>
       <c r="BS17" s="36"/>
       <c r="BT17" s="36"/>
       <c r="BU17" s="36"/>
@@ -2347,28 +2476,37 @@
       <c r="BX17" s="36"/>
       <c r="BY17" s="36"/>
       <c r="BZ17" s="36"/>
+      <c r="CA17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C18" s="39"/>
       <c r="D18" s="35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
+        <v>38</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="K18" s="36"/>
       <c r="L18" s="36"/>
       <c r="M18" s="36"/>
@@ -2379,9 +2517,9 @@
       <c r="R18" s="36"/>
       <c r="S18" s="36"/>
       <c r="T18" s="36"/>
-      <c r="U18" s="37"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="36"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="37"/>
+      <c r="W18" s="38"/>
       <c r="X18" s="36"/>
       <c r="Y18" s="36"/>
       <c r="Z18" s="36"/>
@@ -2397,9 +2535,9 @@
       <c r="AJ18" s="36"/>
       <c r="AK18" s="36"/>
       <c r="AL18" s="36"/>
-      <c r="AM18" s="37"/>
-      <c r="AN18" s="38"/>
-      <c r="AO18" s="36"/>
+      <c r="AM18" s="36"/>
+      <c r="AN18" s="37"/>
+      <c r="AO18" s="38"/>
       <c r="AP18" s="36"/>
       <c r="AQ18" s="36"/>
       <c r="AR18" s="36"/>
@@ -2407,9 +2545,9 @@
       <c r="AT18" s="36"/>
       <c r="AU18" s="36"/>
       <c r="AV18" s="36"/>
-      <c r="AW18" s="37"/>
-      <c r="AX18" s="38"/>
-      <c r="AY18" s="36"/>
+      <c r="AW18" s="36"/>
+      <c r="AX18" s="37"/>
+      <c r="AY18" s="38"/>
       <c r="AZ18" s="36"/>
       <c r="BA18" s="36"/>
       <c r="BB18" s="36"/>
@@ -2426,9 +2564,9 @@
       <c r="BM18" s="36"/>
       <c r="BN18" s="36"/>
       <c r="BO18" s="36"/>
-      <c r="BP18" s="37"/>
-      <c r="BQ18" s="38"/>
-      <c r="BR18" s="36"/>
+      <c r="BP18" s="36"/>
+      <c r="BQ18" s="37"/>
+      <c r="BR18" s="38"/>
       <c r="BS18" s="36"/>
       <c r="BT18" s="36"/>
       <c r="BU18" s="36"/>
@@ -2437,28 +2575,37 @@
       <c r="BX18" s="36"/>
       <c r="BY18" s="36"/>
       <c r="BZ18" s="36"/>
+      <c r="CA18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C19" s="33"/>
       <c r="D19" s="35" t="n">
         <v>150</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F19" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
+      <c r="G19" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>150</v>
+      </c>
       <c r="K19" s="36"/>
       <c r="L19" s="36"/>
       <c r="M19" s="36"/>
@@ -2469,9 +2616,9 @@
       <c r="R19" s="36"/>
       <c r="S19" s="36"/>
       <c r="T19" s="36"/>
-      <c r="U19" s="37"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="38"/>
       <c r="X19" s="36"/>
       <c r="Y19" s="36"/>
       <c r="Z19" s="36"/>
@@ -2487,9 +2634,9 @@
       <c r="AJ19" s="36"/>
       <c r="AK19" s="36"/>
       <c r="AL19" s="36"/>
-      <c r="AM19" s="37"/>
-      <c r="AN19" s="38"/>
-      <c r="AO19" s="36"/>
+      <c r="AM19" s="36"/>
+      <c r="AN19" s="37"/>
+      <c r="AO19" s="38"/>
       <c r="AP19" s="36"/>
       <c r="AQ19" s="36"/>
       <c r="AR19" s="36"/>
@@ -2497,9 +2644,9 @@
       <c r="AT19" s="36"/>
       <c r="AU19" s="36"/>
       <c r="AV19" s="36"/>
-      <c r="AW19" s="37"/>
-      <c r="AX19" s="38"/>
-      <c r="AY19" s="36"/>
+      <c r="AW19" s="36"/>
+      <c r="AX19" s="37"/>
+      <c r="AY19" s="38"/>
       <c r="AZ19" s="36"/>
       <c r="BA19" s="36"/>
       <c r="BB19" s="36"/>
@@ -2516,9 +2663,9 @@
       <c r="BM19" s="36"/>
       <c r="BN19" s="36"/>
       <c r="BO19" s="36"/>
-      <c r="BP19" s="37"/>
-      <c r="BQ19" s="38"/>
-      <c r="BR19" s="36"/>
+      <c r="BP19" s="36"/>
+      <c r="BQ19" s="37"/>
+      <c r="BR19" s="38"/>
       <c r="BS19" s="36"/>
       <c r="BT19" s="36"/>
       <c r="BU19" s="36"/>
@@ -2527,28 +2674,37 @@
       <c r="BX19" s="36"/>
       <c r="BY19" s="36"/>
       <c r="BZ19" s="36"/>
+      <c r="CA19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C20" s="33"/>
       <c r="D20" s="35" t="n">
         <v>55</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F20" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
+      <c r="G20" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="I20" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="K20" s="36"/>
       <c r="L20" s="36"/>
       <c r="M20" s="36"/>
@@ -2559,9 +2715,9 @@
       <c r="R20" s="36"/>
       <c r="S20" s="36"/>
       <c r="T20" s="36"/>
-      <c r="U20" s="37"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="38"/>
       <c r="X20" s="36"/>
       <c r="Y20" s="36"/>
       <c r="Z20" s="36"/>
@@ -2577,9 +2733,9 @@
       <c r="AJ20" s="36"/>
       <c r="AK20" s="36"/>
       <c r="AL20" s="36"/>
-      <c r="AM20" s="37"/>
-      <c r="AN20" s="38"/>
-      <c r="AO20" s="36"/>
+      <c r="AM20" s="36"/>
+      <c r="AN20" s="37"/>
+      <c r="AO20" s="38"/>
       <c r="AP20" s="36"/>
       <c r="AQ20" s="36"/>
       <c r="AR20" s="36"/>
@@ -2587,9 +2743,9 @@
       <c r="AT20" s="36"/>
       <c r="AU20" s="36"/>
       <c r="AV20" s="36"/>
-      <c r="AW20" s="37"/>
-      <c r="AX20" s="38"/>
-      <c r="AY20" s="36"/>
+      <c r="AW20" s="36"/>
+      <c r="AX20" s="37"/>
+      <c r="AY20" s="38"/>
       <c r="AZ20" s="36"/>
       <c r="BA20" s="36"/>
       <c r="BB20" s="36"/>
@@ -2606,9 +2762,9 @@
       <c r="BM20" s="36"/>
       <c r="BN20" s="36"/>
       <c r="BO20" s="36"/>
-      <c r="BP20" s="37"/>
-      <c r="BQ20" s="38"/>
-      <c r="BR20" s="36"/>
+      <c r="BP20" s="36"/>
+      <c r="BQ20" s="37"/>
+      <c r="BR20" s="38"/>
       <c r="BS20" s="36"/>
       <c r="BT20" s="36"/>
       <c r="BU20" s="36"/>
@@ -2617,28 +2773,37 @@
       <c r="BX20" s="36"/>
       <c r="BY20" s="36"/>
       <c r="BZ20" s="36"/>
+      <c r="CA20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C21" s="39"/>
       <c r="D21" s="35" t="n">
         <v>72</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F21" s="35" t="n">
         <v>72</v>
       </c>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
+      <c r="G21" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>72</v>
+      </c>
       <c r="K21" s="36"/>
       <c r="L21" s="36"/>
       <c r="M21" s="36"/>
@@ -2649,9 +2814,9 @@
       <c r="R21" s="36"/>
       <c r="S21" s="36"/>
       <c r="T21" s="36"/>
-      <c r="U21" s="37"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="38"/>
       <c r="X21" s="36"/>
       <c r="Y21" s="36"/>
       <c r="Z21" s="36"/>
@@ -2667,9 +2832,9 @@
       <c r="AJ21" s="36"/>
       <c r="AK21" s="36"/>
       <c r="AL21" s="36"/>
-      <c r="AM21" s="37"/>
-      <c r="AN21" s="38"/>
-      <c r="AO21" s="36"/>
+      <c r="AM21" s="36"/>
+      <c r="AN21" s="37"/>
+      <c r="AO21" s="38"/>
       <c r="AP21" s="36"/>
       <c r="AQ21" s="36"/>
       <c r="AR21" s="36"/>
@@ -2677,9 +2842,9 @@
       <c r="AT21" s="36"/>
       <c r="AU21" s="36"/>
       <c r="AV21" s="36"/>
-      <c r="AW21" s="37"/>
-      <c r="AX21" s="38"/>
-      <c r="AY21" s="36"/>
+      <c r="AW21" s="36"/>
+      <c r="AX21" s="37"/>
+      <c r="AY21" s="38"/>
       <c r="AZ21" s="36"/>
       <c r="BA21" s="36"/>
       <c r="BB21" s="36"/>
@@ -2696,9 +2861,9 @@
       <c r="BM21" s="36"/>
       <c r="BN21" s="36"/>
       <c r="BO21" s="36"/>
-      <c r="BP21" s="37"/>
-      <c r="BQ21" s="38"/>
-      <c r="BR21" s="36"/>
+      <c r="BP21" s="36"/>
+      <c r="BQ21" s="37"/>
+      <c r="BR21" s="38"/>
       <c r="BS21" s="36"/>
       <c r="BT21" s="36"/>
       <c r="BU21" s="36"/>
@@ -2707,28 +2872,37 @@
       <c r="BX21" s="36"/>
       <c r="BY21" s="36"/>
       <c r="BZ21" s="36"/>
+      <c r="CA21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C22" s="39"/>
       <c r="D22" s="35" t="n">
         <v>400</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F22" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
+      <c r="G22" s="35" t="n">
+        <v>400</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>400</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>400</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>400</v>
+      </c>
       <c r="K22" s="36"/>
       <c r="L22" s="36"/>
       <c r="M22" s="36"/>
@@ -2739,9 +2913,9 @@
       <c r="R22" s="36"/>
       <c r="S22" s="36"/>
       <c r="T22" s="36"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="37"/>
+      <c r="W22" s="38"/>
       <c r="X22" s="36"/>
       <c r="Y22" s="36"/>
       <c r="Z22" s="36"/>
@@ -2757,9 +2931,9 @@
       <c r="AJ22" s="36"/>
       <c r="AK22" s="36"/>
       <c r="AL22" s="36"/>
-      <c r="AM22" s="37"/>
-      <c r="AN22" s="38"/>
-      <c r="AO22" s="36"/>
+      <c r="AM22" s="36"/>
+      <c r="AN22" s="37"/>
+      <c r="AO22" s="38"/>
       <c r="AP22" s="36"/>
       <c r="AQ22" s="36"/>
       <c r="AR22" s="36"/>
@@ -2767,9 +2941,9 @@
       <c r="AT22" s="36"/>
       <c r="AU22" s="36"/>
       <c r="AV22" s="36"/>
-      <c r="AW22" s="37"/>
-      <c r="AX22" s="38"/>
-      <c r="AY22" s="36"/>
+      <c r="AW22" s="36"/>
+      <c r="AX22" s="37"/>
+      <c r="AY22" s="38"/>
       <c r="AZ22" s="36"/>
       <c r="BA22" s="36"/>
       <c r="BB22" s="36"/>
@@ -2786,9 +2960,9 @@
       <c r="BM22" s="36"/>
       <c r="BN22" s="36"/>
       <c r="BO22" s="36"/>
-      <c r="BP22" s="37"/>
-      <c r="BQ22" s="38"/>
-      <c r="BR22" s="36"/>
+      <c r="BP22" s="36"/>
+      <c r="BQ22" s="37"/>
+      <c r="BR22" s="38"/>
       <c r="BS22" s="36"/>
       <c r="BT22" s="36"/>
       <c r="BU22" s="36"/>
@@ -2797,28 +2971,37 @@
       <c r="BX22" s="36"/>
       <c r="BY22" s="36"/>
       <c r="BZ22" s="36"/>
+      <c r="CA22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C23" s="33"/>
       <c r="D23" s="35" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
+        <v>55</v>
+      </c>
+      <c r="G23" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="35" t="s">
+        <v>55</v>
+      </c>
       <c r="K23" s="36"/>
       <c r="L23" s="36"/>
       <c r="M23" s="36"/>
@@ -2829,9 +3012,9 @@
       <c r="R23" s="36"/>
       <c r="S23" s="36"/>
       <c r="T23" s="36"/>
-      <c r="U23" s="37"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="38"/>
       <c r="X23" s="36"/>
       <c r="Y23" s="36"/>
       <c r="Z23" s="36"/>
@@ -2847,9 +3030,9 @@
       <c r="AJ23" s="36"/>
       <c r="AK23" s="36"/>
       <c r="AL23" s="36"/>
-      <c r="AM23" s="37"/>
-      <c r="AN23" s="38"/>
-      <c r="AO23" s="36"/>
+      <c r="AM23" s="36"/>
+      <c r="AN23" s="37"/>
+      <c r="AO23" s="38"/>
       <c r="AP23" s="36"/>
       <c r="AQ23" s="36"/>
       <c r="AR23" s="36"/>
@@ -2857,9 +3040,9 @@
       <c r="AT23" s="36"/>
       <c r="AU23" s="36"/>
       <c r="AV23" s="36"/>
-      <c r="AW23" s="37"/>
-      <c r="AX23" s="38"/>
-      <c r="AY23" s="36"/>
+      <c r="AW23" s="36"/>
+      <c r="AX23" s="37"/>
+      <c r="AY23" s="38"/>
       <c r="AZ23" s="36"/>
       <c r="BA23" s="36"/>
       <c r="BB23" s="36"/>
@@ -2876,9 +3059,9 @@
       <c r="BM23" s="36"/>
       <c r="BN23" s="36"/>
       <c r="BO23" s="36"/>
-      <c r="BP23" s="37"/>
-      <c r="BQ23" s="38"/>
-      <c r="BR23" s="36"/>
+      <c r="BP23" s="36"/>
+      <c r="BQ23" s="37"/>
+      <c r="BR23" s="38"/>
       <c r="BS23" s="36"/>
       <c r="BT23" s="36"/>
       <c r="BU23" s="36"/>
@@ -2887,28 +3070,37 @@
       <c r="BX23" s="36"/>
       <c r="BY23" s="36"/>
       <c r="BZ23" s="36"/>
+      <c r="CA23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C24" s="33"/>
       <c r="D24" s="35" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
+        <v>59</v>
+      </c>
+      <c r="G24" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>59</v>
+      </c>
       <c r="K24" s="36"/>
       <c r="L24" s="36"/>
       <c r="M24" s="36"/>
@@ -2919,9 +3111,9 @@
       <c r="R24" s="36"/>
       <c r="S24" s="36"/>
       <c r="T24" s="36"/>
-      <c r="U24" s="37"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="38"/>
       <c r="X24" s="36"/>
       <c r="Y24" s="36"/>
       <c r="Z24" s="36"/>
@@ -2937,9 +3129,9 @@
       <c r="AJ24" s="36"/>
       <c r="AK24" s="36"/>
       <c r="AL24" s="36"/>
-      <c r="AM24" s="37"/>
-      <c r="AN24" s="38"/>
-      <c r="AO24" s="36"/>
+      <c r="AM24" s="36"/>
+      <c r="AN24" s="37"/>
+      <c r="AO24" s="38"/>
       <c r="AP24" s="36"/>
       <c r="AQ24" s="36"/>
       <c r="AR24" s="36"/>
@@ -2947,9 +3139,9 @@
       <c r="AT24" s="36"/>
       <c r="AU24" s="36"/>
       <c r="AV24" s="36"/>
-      <c r="AW24" s="37"/>
-      <c r="AX24" s="38"/>
-      <c r="AY24" s="36"/>
+      <c r="AW24" s="36"/>
+      <c r="AX24" s="37"/>
+      <c r="AY24" s="38"/>
       <c r="AZ24" s="36"/>
       <c r="BA24" s="36"/>
       <c r="BB24" s="36"/>
@@ -2966,9 +3158,9 @@
       <c r="BM24" s="36"/>
       <c r="BN24" s="36"/>
       <c r="BO24" s="36"/>
-      <c r="BP24" s="37"/>
-      <c r="BQ24" s="38"/>
-      <c r="BR24" s="36"/>
+      <c r="BP24" s="36"/>
+      <c r="BQ24" s="37"/>
+      <c r="BR24" s="38"/>
       <c r="BS24" s="36"/>
       <c r="BT24" s="36"/>
       <c r="BU24" s="36"/>
@@ -2977,28 +3169,37 @@
       <c r="BX24" s="36"/>
       <c r="BY24" s="36"/>
       <c r="BZ24" s="36"/>
+      <c r="CA24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F25" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
+      <c r="G25" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" s="36"/>
       <c r="L25" s="36"/>
       <c r="M25" s="36"/>
@@ -3009,9 +3210,9 @@
       <c r="R25" s="36"/>
       <c r="S25" s="36"/>
       <c r="T25" s="36"/>
-      <c r="U25" s="37"/>
-      <c r="V25" s="38"/>
-      <c r="W25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="38"/>
       <c r="X25" s="36"/>
       <c r="Y25" s="36"/>
       <c r="Z25" s="36"/>
@@ -3027,9 +3228,9 @@
       <c r="AJ25" s="36"/>
       <c r="AK25" s="36"/>
       <c r="AL25" s="36"/>
-      <c r="AM25" s="37"/>
-      <c r="AN25" s="38"/>
-      <c r="AO25" s="36"/>
+      <c r="AM25" s="36"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="38"/>
       <c r="AP25" s="36"/>
       <c r="AQ25" s="36"/>
       <c r="AR25" s="36"/>
@@ -3037,9 +3238,9 @@
       <c r="AT25" s="36"/>
       <c r="AU25" s="36"/>
       <c r="AV25" s="36"/>
-      <c r="AW25" s="37"/>
-      <c r="AX25" s="38"/>
-      <c r="AY25" s="36"/>
+      <c r="AW25" s="36"/>
+      <c r="AX25" s="37"/>
+      <c r="AY25" s="38"/>
       <c r="AZ25" s="36"/>
       <c r="BA25" s="36"/>
       <c r="BB25" s="36"/>
@@ -3056,9 +3257,9 @@
       <c r="BM25" s="36"/>
       <c r="BN25" s="36"/>
       <c r="BO25" s="36"/>
-      <c r="BP25" s="37"/>
-      <c r="BQ25" s="38"/>
-      <c r="BR25" s="36"/>
+      <c r="BP25" s="36"/>
+      <c r="BQ25" s="37"/>
+      <c r="BR25" s="38"/>
       <c r="BS25" s="36"/>
       <c r="BT25" s="36"/>
       <c r="BU25" s="36"/>
@@ -3067,28 +3268,37 @@
       <c r="BX25" s="36"/>
       <c r="BY25" s="36"/>
       <c r="BZ25" s="36"/>
+      <c r="CA25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F26" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
+      <c r="G26" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" s="36"/>
       <c r="L26" s="36"/>
       <c r="M26" s="36"/>
@@ -3099,9 +3309,9 @@
       <c r="R26" s="36"/>
       <c r="S26" s="36"/>
       <c r="T26" s="36"/>
-      <c r="U26" s="37"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="37"/>
+      <c r="W26" s="38"/>
       <c r="X26" s="36"/>
       <c r="Y26" s="36"/>
       <c r="Z26" s="36"/>
@@ -3117,9 +3327,9 @@
       <c r="AJ26" s="36"/>
       <c r="AK26" s="36"/>
       <c r="AL26" s="36"/>
-      <c r="AM26" s="37"/>
-      <c r="AN26" s="38"/>
-      <c r="AO26" s="36"/>
+      <c r="AM26" s="36"/>
+      <c r="AN26" s="37"/>
+      <c r="AO26" s="38"/>
       <c r="AP26" s="36"/>
       <c r="AQ26" s="36"/>
       <c r="AR26" s="36"/>
@@ -3127,9 +3337,9 @@
       <c r="AT26" s="36"/>
       <c r="AU26" s="36"/>
       <c r="AV26" s="36"/>
-      <c r="AW26" s="37"/>
-      <c r="AX26" s="38"/>
-      <c r="AY26" s="36"/>
+      <c r="AW26" s="36"/>
+      <c r="AX26" s="37"/>
+      <c r="AY26" s="38"/>
       <c r="AZ26" s="36"/>
       <c r="BA26" s="36"/>
       <c r="BB26" s="36"/>
@@ -3146,9 +3356,9 @@
       <c r="BM26" s="36"/>
       <c r="BN26" s="36"/>
       <c r="BO26" s="36"/>
-      <c r="BP26" s="37"/>
-      <c r="BQ26" s="38"/>
-      <c r="BR26" s="36"/>
+      <c r="BP26" s="36"/>
+      <c r="BQ26" s="37"/>
+      <c r="BR26" s="38"/>
       <c r="BS26" s="36"/>
       <c r="BT26" s="36"/>
       <c r="BU26" s="36"/>
@@ -3157,28 +3367,37 @@
       <c r="BX26" s="36"/>
       <c r="BY26" s="36"/>
       <c r="BZ26" s="36"/>
+      <c r="CA26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C27" s="33"/>
       <c r="D27" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F27" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
+      <c r="G27" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" s="36"/>
       <c r="L27" s="36"/>
       <c r="M27" s="36"/>
@@ -3189,9 +3408,9 @@
       <c r="R27" s="36"/>
       <c r="S27" s="36"/>
       <c r="T27" s="36"/>
-      <c r="U27" s="37"/>
-      <c r="V27" s="38"/>
-      <c r="W27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="38"/>
       <c r="X27" s="36"/>
       <c r="Y27" s="36"/>
       <c r="Z27" s="36"/>
@@ -3207,9 +3426,9 @@
       <c r="AJ27" s="36"/>
       <c r="AK27" s="36"/>
       <c r="AL27" s="36"/>
-      <c r="AM27" s="37"/>
-      <c r="AN27" s="38"/>
-      <c r="AO27" s="36"/>
+      <c r="AM27" s="36"/>
+      <c r="AN27" s="37"/>
+      <c r="AO27" s="38"/>
       <c r="AP27" s="36"/>
       <c r="AQ27" s="36"/>
       <c r="AR27" s="36"/>
@@ -3217,9 +3436,9 @@
       <c r="AT27" s="36"/>
       <c r="AU27" s="36"/>
       <c r="AV27" s="36"/>
-      <c r="AW27" s="37"/>
-      <c r="AX27" s="38"/>
-      <c r="AY27" s="36"/>
+      <c r="AW27" s="36"/>
+      <c r="AX27" s="37"/>
+      <c r="AY27" s="38"/>
       <c r="AZ27" s="36"/>
       <c r="BA27" s="36"/>
       <c r="BB27" s="36"/>
@@ -3236,9 +3455,9 @@
       <c r="BM27" s="36"/>
       <c r="BN27" s="36"/>
       <c r="BO27" s="36"/>
-      <c r="BP27" s="37"/>
-      <c r="BQ27" s="38"/>
-      <c r="BR27" s="36"/>
+      <c r="BP27" s="36"/>
+      <c r="BQ27" s="37"/>
+      <c r="BR27" s="38"/>
       <c r="BS27" s="36"/>
       <c r="BT27" s="36"/>
       <c r="BU27" s="36"/>
@@ -3247,28 +3466,37 @@
       <c r="BX27" s="36"/>
       <c r="BY27" s="36"/>
       <c r="BZ27" s="36"/>
+      <c r="CA27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C28" s="33"/>
       <c r="D28" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F28" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
+      <c r="G28" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" s="36"/>
       <c r="L28" s="36"/>
       <c r="M28" s="36"/>
@@ -3279,9 +3507,9 @@
       <c r="R28" s="36"/>
       <c r="S28" s="36"/>
       <c r="T28" s="36"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="38"/>
       <c r="X28" s="36"/>
       <c r="Y28" s="36"/>
       <c r="Z28" s="36"/>
@@ -3297,9 +3525,9 @@
       <c r="AJ28" s="36"/>
       <c r="AK28" s="36"/>
       <c r="AL28" s="36"/>
-      <c r="AM28" s="37"/>
-      <c r="AN28" s="38"/>
-      <c r="AO28" s="36"/>
+      <c r="AM28" s="36"/>
+      <c r="AN28" s="37"/>
+      <c r="AO28" s="38"/>
       <c r="AP28" s="36"/>
       <c r="AQ28" s="36"/>
       <c r="AR28" s="36"/>
@@ -3307,9 +3535,9 @@
       <c r="AT28" s="36"/>
       <c r="AU28" s="36"/>
       <c r="AV28" s="36"/>
-      <c r="AW28" s="37"/>
-      <c r="AX28" s="38"/>
-      <c r="AY28" s="36"/>
+      <c r="AW28" s="36"/>
+      <c r="AX28" s="37"/>
+      <c r="AY28" s="38"/>
       <c r="AZ28" s="36"/>
       <c r="BA28" s="36"/>
       <c r="BB28" s="36"/>
@@ -3326,9 +3554,9 @@
       <c r="BM28" s="36"/>
       <c r="BN28" s="36"/>
       <c r="BO28" s="36"/>
-      <c r="BP28" s="37"/>
-      <c r="BQ28" s="38"/>
-      <c r="BR28" s="36"/>
+      <c r="BP28" s="36"/>
+      <c r="BQ28" s="37"/>
+      <c r="BR28" s="38"/>
       <c r="BS28" s="36"/>
       <c r="BT28" s="36"/>
       <c r="BU28" s="36"/>
@@ -3337,28 +3565,37 @@
       <c r="BX28" s="36"/>
       <c r="BY28" s="36"/>
       <c r="BZ28" s="36"/>
+      <c r="CA28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
+        <v>75</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="35" t="s">
+        <v>75</v>
+      </c>
       <c r="K29" s="36"/>
       <c r="L29" s="36"/>
       <c r="M29" s="36"/>
@@ -3369,9 +3606,9 @@
       <c r="R29" s="36"/>
       <c r="S29" s="36"/>
       <c r="T29" s="36"/>
-      <c r="U29" s="37"/>
-      <c r="V29" s="38"/>
-      <c r="W29" s="36"/>
+      <c r="U29" s="36"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="38"/>
       <c r="X29" s="36"/>
       <c r="Y29" s="36"/>
       <c r="Z29" s="36"/>
@@ -3387,9 +3624,9 @@
       <c r="AJ29" s="36"/>
       <c r="AK29" s="36"/>
       <c r="AL29" s="36"/>
-      <c r="AM29" s="37"/>
-      <c r="AN29" s="38"/>
-      <c r="AO29" s="36"/>
+      <c r="AM29" s="36"/>
+      <c r="AN29" s="37"/>
+      <c r="AO29" s="38"/>
       <c r="AP29" s="36"/>
       <c r="AQ29" s="36"/>
       <c r="AR29" s="36"/>
@@ -3397,9 +3634,9 @@
       <c r="AT29" s="36"/>
       <c r="AU29" s="36"/>
       <c r="AV29" s="36"/>
-      <c r="AW29" s="37"/>
-      <c r="AX29" s="38"/>
-      <c r="AY29" s="36"/>
+      <c r="AW29" s="36"/>
+      <c r="AX29" s="37"/>
+      <c r="AY29" s="38"/>
       <c r="AZ29" s="36"/>
       <c r="BA29" s="36"/>
       <c r="BB29" s="36"/>
@@ -3416,9 +3653,9 @@
       <c r="BM29" s="36"/>
       <c r="BN29" s="36"/>
       <c r="BO29" s="36"/>
-      <c r="BP29" s="37"/>
-      <c r="BQ29" s="38"/>
-      <c r="BR29" s="36"/>
+      <c r="BP29" s="36"/>
+      <c r="BQ29" s="37"/>
+      <c r="BR29" s="38"/>
       <c r="BS29" s="36"/>
       <c r="BT29" s="36"/>
       <c r="BU29" s="36"/>
@@ -3427,13 +3664,14 @@
       <c r="BX29" s="36"/>
       <c r="BY29" s="36"/>
       <c r="BZ29" s="36"/>
+      <c r="CA29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="35" t="n">
@@ -3443,12 +3681,20 @@
         <v>55</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
+        <v>78</v>
+      </c>
+      <c r="G30" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="35" t="s">
+        <v>78</v>
+      </c>
       <c r="K30" s="36"/>
       <c r="L30" s="36"/>
       <c r="M30" s="36"/>
@@ -3459,9 +3705,9 @@
       <c r="R30" s="36"/>
       <c r="S30" s="36"/>
       <c r="T30" s="36"/>
-      <c r="U30" s="37"/>
-      <c r="V30" s="38"/>
-      <c r="W30" s="36"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="38"/>
       <c r="X30" s="36"/>
       <c r="Y30" s="36"/>
       <c r="Z30" s="36"/>
@@ -3477,9 +3723,9 @@
       <c r="AJ30" s="36"/>
       <c r="AK30" s="36"/>
       <c r="AL30" s="36"/>
-      <c r="AM30" s="37"/>
-      <c r="AN30" s="38"/>
-      <c r="AO30" s="36"/>
+      <c r="AM30" s="36"/>
+      <c r="AN30" s="37"/>
+      <c r="AO30" s="38"/>
       <c r="AP30" s="36"/>
       <c r="AQ30" s="36"/>
       <c r="AR30" s="36"/>
@@ -3487,9 +3733,9 @@
       <c r="AT30" s="36"/>
       <c r="AU30" s="36"/>
       <c r="AV30" s="36"/>
-      <c r="AW30" s="37"/>
-      <c r="AX30" s="38"/>
-      <c r="AY30" s="36"/>
+      <c r="AW30" s="36"/>
+      <c r="AX30" s="37"/>
+      <c r="AY30" s="38"/>
       <c r="AZ30" s="36"/>
       <c r="BA30" s="36"/>
       <c r="BB30" s="36"/>
@@ -3506,9 +3752,9 @@
       <c r="BM30" s="36"/>
       <c r="BN30" s="36"/>
       <c r="BO30" s="36"/>
-      <c r="BP30" s="37"/>
-      <c r="BQ30" s="38"/>
-      <c r="BR30" s="36"/>
+      <c r="BP30" s="36"/>
+      <c r="BQ30" s="37"/>
+      <c r="BR30" s="38"/>
       <c r="BS30" s="36"/>
       <c r="BT30" s="36"/>
       <c r="BU30" s="36"/>
@@ -3517,13 +3763,14 @@
       <c r="BX30" s="36"/>
       <c r="BY30" s="36"/>
       <c r="BZ30" s="36"/>
+      <c r="CA30" s="36"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="35" t="n">
@@ -3535,10 +3782,18 @@
       <c r="F31" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
+      <c r="G31" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="I31" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="J31" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="K31" s="36"/>
       <c r="L31" s="36"/>
       <c r="M31" s="36"/>
@@ -3549,9 +3804,9 @@
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="36"/>
-      <c r="U31" s="37"/>
-      <c r="V31" s="38"/>
-      <c r="W31" s="36"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="37"/>
+      <c r="W31" s="38"/>
       <c r="X31" s="36"/>
       <c r="Y31" s="36"/>
       <c r="Z31" s="36"/>
@@ -3567,9 +3822,9 @@
       <c r="AJ31" s="36"/>
       <c r="AK31" s="36"/>
       <c r="AL31" s="36"/>
-      <c r="AM31" s="37"/>
-      <c r="AN31" s="38"/>
-      <c r="AO31" s="36"/>
+      <c r="AM31" s="36"/>
+      <c r="AN31" s="37"/>
+      <c r="AO31" s="38"/>
       <c r="AP31" s="36"/>
       <c r="AQ31" s="36"/>
       <c r="AR31" s="36"/>
@@ -3577,9 +3832,9 @@
       <c r="AT31" s="36"/>
       <c r="AU31" s="36"/>
       <c r="AV31" s="36"/>
-      <c r="AW31" s="37"/>
-      <c r="AX31" s="38"/>
-      <c r="AY31" s="36"/>
+      <c r="AW31" s="36"/>
+      <c r="AX31" s="37"/>
+      <c r="AY31" s="38"/>
       <c r="AZ31" s="36"/>
       <c r="BA31" s="36"/>
       <c r="BB31" s="36"/>
@@ -3596,9 +3851,9 @@
       <c r="BM31" s="36"/>
       <c r="BN31" s="36"/>
       <c r="BO31" s="36"/>
-      <c r="BP31" s="37"/>
-      <c r="BQ31" s="38"/>
-      <c r="BR31" s="36"/>
+      <c r="BP31" s="36"/>
+      <c r="BQ31" s="37"/>
+      <c r="BR31" s="38"/>
       <c r="BS31" s="36"/>
       <c r="BT31" s="36"/>
       <c r="BU31" s="36"/>
@@ -3607,28 +3862,37 @@
       <c r="BX31" s="36"/>
       <c r="BY31" s="36"/>
       <c r="BZ31" s="36"/>
+      <c r="CA31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
+        <v>75</v>
+      </c>
+      <c r="G32" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="J32" s="35" t="s">
+        <v>75</v>
+      </c>
       <c r="K32" s="36"/>
       <c r="L32" s="36"/>
       <c r="M32" s="36"/>
@@ -3639,9 +3903,9 @@
       <c r="R32" s="36"/>
       <c r="S32" s="36"/>
       <c r="T32" s="36"/>
-      <c r="U32" s="37"/>
-      <c r="V32" s="38"/>
-      <c r="W32" s="36"/>
+      <c r="U32" s="36"/>
+      <c r="V32" s="37"/>
+      <c r="W32" s="38"/>
       <c r="X32" s="36"/>
       <c r="Y32" s="36"/>
       <c r="Z32" s="36"/>
@@ -3657,9 +3921,9 @@
       <c r="AJ32" s="36"/>
       <c r="AK32" s="36"/>
       <c r="AL32" s="36"/>
-      <c r="AM32" s="37"/>
-      <c r="AN32" s="38"/>
-      <c r="AO32" s="36"/>
+      <c r="AM32" s="36"/>
+      <c r="AN32" s="37"/>
+      <c r="AO32" s="38"/>
       <c r="AP32" s="36"/>
       <c r="AQ32" s="36"/>
       <c r="AR32" s="36"/>
@@ -3667,9 +3931,9 @@
       <c r="AT32" s="36"/>
       <c r="AU32" s="36"/>
       <c r="AV32" s="36"/>
-      <c r="AW32" s="37"/>
-      <c r="AX32" s="38"/>
-      <c r="AY32" s="36"/>
+      <c r="AW32" s="36"/>
+      <c r="AX32" s="37"/>
+      <c r="AY32" s="38"/>
       <c r="AZ32" s="36"/>
       <c r="BA32" s="36"/>
       <c r="BB32" s="36"/>
@@ -3686,9 +3950,9 @@
       <c r="BM32" s="36"/>
       <c r="BN32" s="36"/>
       <c r="BO32" s="36"/>
-      <c r="BP32" s="37"/>
-      <c r="BQ32" s="38"/>
-      <c r="BR32" s="36"/>
+      <c r="BP32" s="36"/>
+      <c r="BQ32" s="37"/>
+      <c r="BR32" s="38"/>
       <c r="BS32" s="36"/>
       <c r="BT32" s="36"/>
       <c r="BU32" s="36"/>
@@ -3697,28 +3961,37 @@
       <c r="BX32" s="36"/>
       <c r="BY32" s="36"/>
       <c r="BZ32" s="36"/>
+      <c r="CA32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="32" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C33" s="39"/>
       <c r="D33" s="35" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E33" s="35" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
+        <v>85</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="35" t="s">
+        <v>85</v>
+      </c>
       <c r="K33" s="36"/>
       <c r="L33" s="36"/>
       <c r="M33" s="36"/>
@@ -3729,9 +4002,9 @@
       <c r="R33" s="36"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
-      <c r="U33" s="37"/>
-      <c r="V33" s="38"/>
-      <c r="W33" s="36"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="37"/>
+      <c r="W33" s="38"/>
       <c r="X33" s="36"/>
       <c r="Y33" s="36"/>
       <c r="Z33" s="36"/>
@@ -3747,9 +4020,9 @@
       <c r="AJ33" s="36"/>
       <c r="AK33" s="36"/>
       <c r="AL33" s="36"/>
-      <c r="AM33" s="37"/>
-      <c r="AN33" s="38"/>
-      <c r="AO33" s="36"/>
+      <c r="AM33" s="36"/>
+      <c r="AN33" s="37"/>
+      <c r="AO33" s="38"/>
       <c r="AP33" s="36"/>
       <c r="AQ33" s="36"/>
       <c r="AR33" s="36"/>
@@ -3757,9 +4030,9 @@
       <c r="AT33" s="36"/>
       <c r="AU33" s="36"/>
       <c r="AV33" s="36"/>
-      <c r="AW33" s="37"/>
-      <c r="AX33" s="38"/>
-      <c r="AY33" s="36"/>
+      <c r="AW33" s="36"/>
+      <c r="AX33" s="37"/>
+      <c r="AY33" s="38"/>
       <c r="AZ33" s="36"/>
       <c r="BA33" s="36"/>
       <c r="BB33" s="36"/>
@@ -3776,9 +4049,9 @@
       <c r="BM33" s="36"/>
       <c r="BN33" s="36"/>
       <c r="BO33" s="36"/>
-      <c r="BP33" s="37"/>
-      <c r="BQ33" s="38"/>
-      <c r="BR33" s="36"/>
+      <c r="BP33" s="36"/>
+      <c r="BQ33" s="37"/>
+      <c r="BR33" s="38"/>
       <c r="BS33" s="36"/>
       <c r="BT33" s="36"/>
       <c r="BU33" s="36"/>
@@ -3787,48 +4060,61 @@
       <c r="BX33" s="36"/>
       <c r="BY33" s="36"/>
       <c r="BZ33" s="36"/>
+      <c r="CA33" s="36"/>
     </row>
     <row r="34" s="42" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="40" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
       <c r="F34" s="41"/>
-      <c r="U34" s="43"/>
-      <c r="V34" s="44"/>
-      <c r="AM34" s="43"/>
-      <c r="AN34" s="44"/>
-      <c r="AW34" s="43"/>
-      <c r="AX34" s="44"/>
-      <c r="BP34" s="43"/>
-      <c r="BQ34" s="44"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="44"/>
+      <c r="AN34" s="43"/>
+      <c r="AO34" s="44"/>
+      <c r="AX34" s="43"/>
+      <c r="AY34" s="44"/>
+      <c r="BQ34" s="43"/>
+      <c r="BR34" s="44"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="32" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="34" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
+        <v>91</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="J35" s="34" t="s">
+        <v>91</v>
+      </c>
       <c r="K35" s="45"/>
       <c r="L35" s="45"/>
       <c r="M35" s="45"/>
@@ -3839,9 +4125,9 @@
       <c r="R35" s="45"/>
       <c r="S35" s="45"/>
       <c r="T35" s="45"/>
-      <c r="U35" s="46"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="45"/>
+      <c r="U35" s="45"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="47"/>
       <c r="X35" s="45"/>
       <c r="Y35" s="45"/>
       <c r="Z35" s="45"/>
@@ -3857,9 +4143,9 @@
       <c r="AJ35" s="45"/>
       <c r="AK35" s="45"/>
       <c r="AL35" s="45"/>
-      <c r="AM35" s="46"/>
-      <c r="AN35" s="47"/>
-      <c r="AO35" s="45"/>
+      <c r="AM35" s="45"/>
+      <c r="AN35" s="46"/>
+      <c r="AO35" s="47"/>
       <c r="AP35" s="45"/>
       <c r="AQ35" s="45"/>
       <c r="AR35" s="45"/>
@@ -3867,9 +4153,9 @@
       <c r="AT35" s="45"/>
       <c r="AU35" s="45"/>
       <c r="AV35" s="45"/>
-      <c r="AW35" s="46"/>
-      <c r="AX35" s="47"/>
-      <c r="AY35" s="45"/>
+      <c r="AW35" s="45"/>
+      <c r="AX35" s="46"/>
+      <c r="AY35" s="47"/>
       <c r="AZ35" s="45"/>
       <c r="BA35" s="45"/>
       <c r="BB35" s="45"/>
@@ -3886,9 +4172,9 @@
       <c r="BM35" s="45"/>
       <c r="BN35" s="45"/>
       <c r="BO35" s="45"/>
-      <c r="BP35" s="46"/>
-      <c r="BQ35" s="47"/>
-      <c r="BR35" s="45"/>
+      <c r="BP35" s="45"/>
+      <c r="BQ35" s="46"/>
+      <c r="BR35" s="47"/>
       <c r="BS35" s="45"/>
       <c r="BT35" s="45"/>
       <c r="BU35" s="45"/>
@@ -3897,22 +4183,31 @@
       <c r="BX35" s="45"/>
       <c r="BY35" s="45"/>
       <c r="BZ35" s="45"/>
+      <c r="CA35" s="45"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
         <v>2</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="34"/>
       <c r="E36" s="34"/>
       <c r="F36" s="34"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
+      <c r="G36" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I36" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J36" s="34" t="s">
+        <v>93</v>
+      </c>
       <c r="K36" s="36"/>
       <c r="L36" s="36"/>
       <c r="M36" s="36"/>
@@ -3923,9 +4218,9 @@
       <c r="R36" s="36"/>
       <c r="S36" s="36"/>
       <c r="T36" s="36"/>
-      <c r="U36" s="37"/>
-      <c r="V36" s="38"/>
-      <c r="W36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="37"/>
+      <c r="W36" s="38"/>
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
@@ -3941,9 +4236,9 @@
       <c r="AJ36" s="36"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="36"/>
-      <c r="AM36" s="37"/>
-      <c r="AN36" s="38"/>
-      <c r="AO36" s="36"/>
+      <c r="AM36" s="36"/>
+      <c r="AN36" s="37"/>
+      <c r="AO36" s="38"/>
       <c r="AP36" s="36"/>
       <c r="AQ36" s="36"/>
       <c r="AR36" s="36"/>
@@ -3951,9 +4246,9 @@
       <c r="AT36" s="36"/>
       <c r="AU36" s="36"/>
       <c r="AV36" s="36"/>
-      <c r="AW36" s="37"/>
-      <c r="AX36" s="38"/>
-      <c r="AY36" s="36"/>
+      <c r="AW36" s="36"/>
+      <c r="AX36" s="37"/>
+      <c r="AY36" s="38"/>
       <c r="AZ36" s="36"/>
       <c r="BA36" s="36"/>
       <c r="BB36" s="36"/>
@@ -3970,9 +4265,9 @@
       <c r="BM36" s="36"/>
       <c r="BN36" s="36"/>
       <c r="BO36" s="36"/>
-      <c r="BP36" s="37"/>
-      <c r="BQ36" s="38"/>
-      <c r="BR36" s="36"/>
+      <c r="BP36" s="36"/>
+      <c r="BQ36" s="37"/>
+      <c r="BR36" s="38"/>
       <c r="BS36" s="36"/>
       <c r="BT36" s="36"/>
       <c r="BU36" s="36"/>
@@ -3981,22 +4276,31 @@
       <c r="BX36" s="36"/>
       <c r="BY36" s="36"/>
       <c r="BZ36" s="36"/>
+      <c r="CA36" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="48" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
+      <c r="G37" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="34" t="s">
+        <v>98</v>
+      </c>
       <c r="K37" s="36"/>
       <c r="L37" s="36"/>
       <c r="M37" s="36"/>
@@ -4007,9 +4311,9 @@
       <c r="R37" s="36"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
-      <c r="U37" s="37"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="36"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="37"/>
+      <c r="W37" s="38"/>
       <c r="X37" s="36"/>
       <c r="Y37" s="36"/>
       <c r="Z37" s="36"/>
@@ -4025,9 +4329,9 @@
       <c r="AJ37" s="36"/>
       <c r="AK37" s="36"/>
       <c r="AL37" s="36"/>
-      <c r="AM37" s="37"/>
-      <c r="AN37" s="38"/>
-      <c r="AO37" s="36"/>
+      <c r="AM37" s="36"/>
+      <c r="AN37" s="37"/>
+      <c r="AO37" s="38"/>
       <c r="AP37" s="36"/>
       <c r="AQ37" s="36"/>
       <c r="AR37" s="36"/>
@@ -4035,9 +4339,9 @@
       <c r="AT37" s="36"/>
       <c r="AU37" s="36"/>
       <c r="AV37" s="36"/>
-      <c r="AW37" s="37"/>
-      <c r="AX37" s="38"/>
-      <c r="AY37" s="36"/>
+      <c r="AW37" s="36"/>
+      <c r="AX37" s="37"/>
+      <c r="AY37" s="38"/>
       <c r="AZ37" s="36"/>
       <c r="BA37" s="36"/>
       <c r="BB37" s="36"/>
@@ -4054,9 +4358,9 @@
       <c r="BM37" s="36"/>
       <c r="BN37" s="36"/>
       <c r="BO37" s="36"/>
-      <c r="BP37" s="37"/>
-      <c r="BQ37" s="38"/>
-      <c r="BR37" s="36"/>
+      <c r="BP37" s="36"/>
+      <c r="BQ37" s="37"/>
+      <c r="BR37" s="38"/>
       <c r="BS37" s="36"/>
       <c r="BT37" s="36"/>
       <c r="BU37" s="36"/>
@@ -4065,32 +4369,37 @@
       <c r="BX37" s="36"/>
       <c r="BY37" s="36"/>
       <c r="BZ37" s="36"/>
+      <c r="CA37" s="36"/>
     </row>
     <row r="38" s="42" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
       <c r="F38" s="41"/>
-      <c r="U38" s="43"/>
-      <c r="V38" s="44"/>
-      <c r="AM38" s="43"/>
-      <c r="AN38" s="44"/>
-      <c r="AW38" s="43"/>
-      <c r="AX38" s="44"/>
-      <c r="BP38" s="43"/>
-      <c r="BQ38" s="44"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="V38" s="43"/>
+      <c r="W38" s="44"/>
+      <c r="AN38" s="43"/>
+      <c r="AO38" s="44"/>
+      <c r="AX38" s="43"/>
+      <c r="AY38" s="44"/>
+      <c r="BQ38" s="43"/>
+      <c r="BR38" s="44"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="32" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>93</v>
@@ -4099,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E39" s="34" t="n">
         <v>70</v>
@@ -4107,10 +4416,18 @@
       <c r="F39" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
+      <c r="G39" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="J39" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="K39" s="36"/>
       <c r="L39" s="36"/>
       <c r="M39" s="36"/>
@@ -4121,8 +4438,8 @@
       <c r="R39" s="36"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
-      <c r="U39" s="37"/>
-      <c r="V39" s="36"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="37"/>
       <c r="W39" s="36"/>
       <c r="X39" s="36"/>
       <c r="Y39" s="36"/>
@@ -4139,8 +4456,8 @@
       <c r="AJ39" s="36"/>
       <c r="AK39" s="36"/>
       <c r="AL39" s="36"/>
-      <c r="AM39" s="37"/>
-      <c r="AN39" s="36"/>
+      <c r="AM39" s="36"/>
+      <c r="AN39" s="37"/>
       <c r="AO39" s="36"/>
       <c r="AP39" s="36"/>
       <c r="AQ39" s="36"/>
@@ -4149,8 +4466,8 @@
       <c r="AT39" s="36"/>
       <c r="AU39" s="36"/>
       <c r="AV39" s="36"/>
-      <c r="AW39" s="37"/>
-      <c r="AX39" s="36"/>
+      <c r="AW39" s="36"/>
+      <c r="AX39" s="37"/>
       <c r="AY39" s="36"/>
       <c r="AZ39" s="36"/>
       <c r="BA39" s="36"/>
@@ -4168,9 +4485,9 @@
       <c r="BM39" s="36"/>
       <c r="BN39" s="36"/>
       <c r="BO39" s="36"/>
-      <c r="BP39" s="37"/>
-      <c r="BQ39" s="38"/>
-      <c r="BR39" s="36"/>
+      <c r="BP39" s="36"/>
+      <c r="BQ39" s="37"/>
+      <c r="BR39" s="38"/>
       <c r="BS39" s="36"/>
       <c r="BT39" s="36"/>
       <c r="BU39" s="36"/>
@@ -4179,19 +4496,20 @@
       <c r="BX39" s="36"/>
       <c r="BY39" s="36"/>
       <c r="BZ39" s="36"/>
+      <c r="CA39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="32" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C40" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E40" s="34" t="n">
         <v>75</v>
@@ -4199,10 +4517,18 @@
       <c r="F40" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
+      <c r="G40" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="J40" s="35" t="n">
+        <v>75</v>
+      </c>
       <c r="K40" s="36"/>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
@@ -4213,8 +4539,8 @@
       <c r="R40" s="36"/>
       <c r="S40" s="36"/>
       <c r="T40" s="36"/>
-      <c r="U40" s="37"/>
-      <c r="V40" s="36"/>
+      <c r="U40" s="36"/>
+      <c r="V40" s="37"/>
       <c r="W40" s="36"/>
       <c r="X40" s="36"/>
       <c r="Y40" s="36"/>
@@ -4231,8 +4557,8 @@
       <c r="AJ40" s="36"/>
       <c r="AK40" s="36"/>
       <c r="AL40" s="36"/>
-      <c r="AM40" s="37"/>
-      <c r="AN40" s="36"/>
+      <c r="AM40" s="36"/>
+      <c r="AN40" s="37"/>
       <c r="AO40" s="36"/>
       <c r="AP40" s="36"/>
       <c r="AQ40" s="36"/>
@@ -4241,8 +4567,8 @@
       <c r="AT40" s="36"/>
       <c r="AU40" s="36"/>
       <c r="AV40" s="36"/>
-      <c r="AW40" s="37"/>
-      <c r="AX40" s="36"/>
+      <c r="AW40" s="36"/>
+      <c r="AX40" s="37"/>
       <c r="AY40" s="36"/>
       <c r="AZ40" s="36"/>
       <c r="BA40" s="36"/>
@@ -4260,9 +4586,9 @@
       <c r="BM40" s="36"/>
       <c r="BN40" s="36"/>
       <c r="BO40" s="36"/>
-      <c r="BP40" s="37"/>
-      <c r="BQ40" s="38"/>
-      <c r="BR40" s="36"/>
+      <c r="BP40" s="36"/>
+      <c r="BQ40" s="37"/>
+      <c r="BR40" s="38"/>
       <c r="BS40" s="36"/>
       <c r="BT40" s="36"/>
       <c r="BU40" s="36"/>
@@ -4271,19 +4597,20 @@
       <c r="BX40" s="36"/>
       <c r="BY40" s="36"/>
       <c r="BZ40" s="36"/>
+      <c r="CA40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="32" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C41" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E41" s="34" t="n">
         <v>60</v>
@@ -4291,10 +4618,18 @@
       <c r="F41" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
+      <c r="G41" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="I41" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="J41" s="35" t="n">
+        <v>60</v>
+      </c>
       <c r="K41" s="36"/>
       <c r="L41" s="36"/>
       <c r="M41" s="36"/>
@@ -4305,8 +4640,8 @@
       <c r="R41" s="36"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
-      <c r="U41" s="37"/>
-      <c r="V41" s="36"/>
+      <c r="U41" s="36"/>
+      <c r="V41" s="37"/>
       <c r="W41" s="36"/>
       <c r="X41" s="36"/>
       <c r="Y41" s="36"/>
@@ -4323,8 +4658,8 @@
       <c r="AJ41" s="36"/>
       <c r="AK41" s="36"/>
       <c r="AL41" s="36"/>
-      <c r="AM41" s="37"/>
-      <c r="AN41" s="36"/>
+      <c r="AM41" s="36"/>
+      <c r="AN41" s="37"/>
       <c r="AO41" s="36"/>
       <c r="AP41" s="36"/>
       <c r="AQ41" s="36"/>
@@ -4333,8 +4668,8 @@
       <c r="AT41" s="36"/>
       <c r="AU41" s="36"/>
       <c r="AV41" s="36"/>
-      <c r="AW41" s="37"/>
-      <c r="AX41" s="36"/>
+      <c r="AW41" s="36"/>
+      <c r="AX41" s="37"/>
       <c r="AY41" s="36"/>
       <c r="AZ41" s="36"/>
       <c r="BA41" s="36"/>
@@ -4352,9 +4687,9 @@
       <c r="BM41" s="36"/>
       <c r="BN41" s="36"/>
       <c r="BO41" s="36"/>
-      <c r="BP41" s="37"/>
-      <c r="BQ41" s="38"/>
-      <c r="BR41" s="36"/>
+      <c r="BP41" s="36"/>
+      <c r="BQ41" s="37"/>
+      <c r="BR41" s="38"/>
       <c r="BS41" s="36"/>
       <c r="BT41" s="36"/>
       <c r="BU41" s="36"/>
@@ -4363,19 +4698,20 @@
       <c r="BX41" s="36"/>
       <c r="BY41" s="36"/>
       <c r="BZ41" s="36"/>
+      <c r="CA41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C42" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E42" s="34" t="n">
         <v>90</v>
@@ -4383,10 +4719,18 @@
       <c r="F42" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
+      <c r="G42" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="I42" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="J42" s="35" t="n">
+        <v>90</v>
+      </c>
       <c r="K42" s="36"/>
       <c r="L42" s="36"/>
       <c r="M42" s="36"/>
@@ -4397,8 +4741,8 @@
       <c r="R42" s="36"/>
       <c r="S42" s="36"/>
       <c r="T42" s="36"/>
-      <c r="U42" s="37"/>
-      <c r="V42" s="36"/>
+      <c r="U42" s="36"/>
+      <c r="V42" s="37"/>
       <c r="W42" s="36"/>
       <c r="X42" s="36"/>
       <c r="Y42" s="36"/>
@@ -4415,8 +4759,8 @@
       <c r="AJ42" s="36"/>
       <c r="AK42" s="36"/>
       <c r="AL42" s="36"/>
-      <c r="AM42" s="37"/>
-      <c r="AN42" s="36"/>
+      <c r="AM42" s="36"/>
+      <c r="AN42" s="37"/>
       <c r="AO42" s="36"/>
       <c r="AP42" s="36"/>
       <c r="AQ42" s="36"/>
@@ -4425,8 +4769,8 @@
       <c r="AT42" s="36"/>
       <c r="AU42" s="36"/>
       <c r="AV42" s="36"/>
-      <c r="AW42" s="37"/>
-      <c r="AX42" s="36"/>
+      <c r="AW42" s="36"/>
+      <c r="AX42" s="37"/>
       <c r="AY42" s="36"/>
       <c r="AZ42" s="36"/>
       <c r="BA42" s="36"/>
@@ -4444,9 +4788,9 @@
       <c r="BM42" s="36"/>
       <c r="BN42" s="36"/>
       <c r="BO42" s="36"/>
-      <c r="BP42" s="37"/>
-      <c r="BQ42" s="38"/>
-      <c r="BR42" s="36"/>
+      <c r="BP42" s="36"/>
+      <c r="BQ42" s="37"/>
+      <c r="BR42" s="38"/>
       <c r="BS42" s="36"/>
       <c r="BT42" s="36"/>
       <c r="BU42" s="36"/>
@@ -4455,19 +4799,20 @@
       <c r="BX42" s="36"/>
       <c r="BY42" s="36"/>
       <c r="BZ42" s="36"/>
+      <c r="CA42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C43" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E43" s="34" t="n">
         <v>1000</v>
@@ -4475,10 +4820,18 @@
       <c r="F43" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
+      <c r="G43" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I43" s="35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J43" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
       <c r="M43" s="36"/>
@@ -4489,8 +4842,8 @@
       <c r="R43" s="36"/>
       <c r="S43" s="36"/>
       <c r="T43" s="36"/>
-      <c r="U43" s="37"/>
-      <c r="V43" s="36"/>
+      <c r="U43" s="36"/>
+      <c r="V43" s="37"/>
       <c r="W43" s="36"/>
       <c r="X43" s="36"/>
       <c r="Y43" s="36"/>
@@ -4507,8 +4860,8 @@
       <c r="AJ43" s="36"/>
       <c r="AK43" s="36"/>
       <c r="AL43" s="36"/>
-      <c r="AM43" s="37"/>
-      <c r="AN43" s="36"/>
+      <c r="AM43" s="36"/>
+      <c r="AN43" s="37"/>
       <c r="AO43" s="36"/>
       <c r="AP43" s="36"/>
       <c r="AQ43" s="36"/>
@@ -4517,8 +4870,8 @@
       <c r="AT43" s="36"/>
       <c r="AU43" s="36"/>
       <c r="AV43" s="36"/>
-      <c r="AW43" s="37"/>
-      <c r="AX43" s="36"/>
+      <c r="AW43" s="36"/>
+      <c r="AX43" s="37"/>
       <c r="AY43" s="36"/>
       <c r="AZ43" s="36"/>
       <c r="BA43" s="36"/>
@@ -4536,9 +4889,9 @@
       <c r="BM43" s="36"/>
       <c r="BN43" s="36"/>
       <c r="BO43" s="36"/>
-      <c r="BP43" s="37"/>
-      <c r="BQ43" s="38"/>
-      <c r="BR43" s="36"/>
+      <c r="BP43" s="36"/>
+      <c r="BQ43" s="37"/>
+      <c r="BR43" s="38"/>
       <c r="BS43" s="36"/>
       <c r="BT43" s="36"/>
       <c r="BU43" s="36"/>
@@ -4547,19 +4900,20 @@
       <c r="BX43" s="36"/>
       <c r="BY43" s="36"/>
       <c r="BZ43" s="36"/>
+      <c r="CA43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="32" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C44" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E44" s="34" t="n">
         <v>75</v>
@@ -4567,10 +4921,18 @@
       <c r="F44" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
+      <c r="G44" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="H44" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="I44" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="J44" s="35" t="n">
+        <v>500</v>
+      </c>
       <c r="K44" s="36"/>
       <c r="L44" s="36"/>
       <c r="M44" s="36"/>
@@ -4581,8 +4943,8 @@
       <c r="R44" s="36"/>
       <c r="S44" s="36"/>
       <c r="T44" s="36"/>
-      <c r="U44" s="37"/>
-      <c r="V44" s="36"/>
+      <c r="U44" s="36"/>
+      <c r="V44" s="37"/>
       <c r="W44" s="36"/>
       <c r="X44" s="36"/>
       <c r="Y44" s="36"/>
@@ -4599,8 +4961,8 @@
       <c r="AJ44" s="36"/>
       <c r="AK44" s="36"/>
       <c r="AL44" s="36"/>
-      <c r="AM44" s="37"/>
-      <c r="AN44" s="36"/>
+      <c r="AM44" s="36"/>
+      <c r="AN44" s="37"/>
       <c r="AO44" s="36"/>
       <c r="AP44" s="36"/>
       <c r="AQ44" s="36"/>
@@ -4609,8 +4971,8 @@
       <c r="AT44" s="36"/>
       <c r="AU44" s="36"/>
       <c r="AV44" s="36"/>
-      <c r="AW44" s="37"/>
-      <c r="AX44" s="36"/>
+      <c r="AW44" s="36"/>
+      <c r="AX44" s="37"/>
       <c r="AY44" s="36"/>
       <c r="AZ44" s="36"/>
       <c r="BA44" s="36"/>
@@ -4628,9 +4990,9 @@
       <c r="BM44" s="36"/>
       <c r="BN44" s="36"/>
       <c r="BO44" s="36"/>
-      <c r="BP44" s="37"/>
-      <c r="BQ44" s="38"/>
-      <c r="BR44" s="36"/>
+      <c r="BP44" s="36"/>
+      <c r="BQ44" s="37"/>
+      <c r="BR44" s="38"/>
       <c r="BS44" s="36"/>
       <c r="BT44" s="36"/>
       <c r="BU44" s="36"/>
@@ -4639,19 +5001,20 @@
       <c r="BX44" s="36"/>
       <c r="BY44" s="36"/>
       <c r="BZ44" s="36"/>
+      <c r="CA44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C45" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E45" s="34" t="n">
         <v>100</v>
@@ -4659,10 +5022,18 @@
       <c r="F45" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="G45" s="36"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="36"/>
-      <c r="J45" s="36"/>
+      <c r="G45" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" s="35" t="n">
+        <v>100</v>
+      </c>
       <c r="K45" s="36"/>
       <c r="L45" s="36"/>
       <c r="M45" s="36"/>
@@ -4673,8 +5044,8 @@
       <c r="R45" s="36"/>
       <c r="S45" s="36"/>
       <c r="T45" s="36"/>
-      <c r="U45" s="37"/>
-      <c r="V45" s="36"/>
+      <c r="U45" s="36"/>
+      <c r="V45" s="37"/>
       <c r="W45" s="36"/>
       <c r="X45" s="36"/>
       <c r="Y45" s="36"/>
@@ -4691,8 +5062,8 @@
       <c r="AJ45" s="36"/>
       <c r="AK45" s="36"/>
       <c r="AL45" s="36"/>
-      <c r="AM45" s="37"/>
-      <c r="AN45" s="36"/>
+      <c r="AM45" s="36"/>
+      <c r="AN45" s="37"/>
       <c r="AO45" s="36"/>
       <c r="AP45" s="36"/>
       <c r="AQ45" s="36"/>
@@ -4701,8 +5072,8 @@
       <c r="AT45" s="36"/>
       <c r="AU45" s="36"/>
       <c r="AV45" s="36"/>
-      <c r="AW45" s="37"/>
-      <c r="AX45" s="36"/>
+      <c r="AW45" s="36"/>
+      <c r="AX45" s="37"/>
       <c r="AY45" s="36"/>
       <c r="AZ45" s="36"/>
       <c r="BA45" s="36"/>
@@ -4720,9 +5091,9 @@
       <c r="BM45" s="36"/>
       <c r="BN45" s="36"/>
       <c r="BO45" s="36"/>
-      <c r="BP45" s="37"/>
-      <c r="BQ45" s="38"/>
-      <c r="BR45" s="36"/>
+      <c r="BP45" s="36"/>
+      <c r="BQ45" s="37"/>
+      <c r="BR45" s="38"/>
       <c r="BS45" s="36"/>
       <c r="BT45" s="36"/>
       <c r="BU45" s="36"/>
@@ -4731,19 +5102,20 @@
       <c r="BX45" s="36"/>
       <c r="BY45" s="36"/>
       <c r="BZ45" s="36"/>
+      <c r="CA45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C46" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E46" s="34" t="n">
         <v>72</v>
@@ -4751,10 +5123,18 @@
       <c r="F46" s="35" t="n">
         <v>200</v>
       </c>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
+      <c r="G46" s="35" t="n">
+        <v>200</v>
+      </c>
+      <c r="H46" s="35" t="n">
+        <v>200</v>
+      </c>
+      <c r="I46" s="35" t="n">
+        <v>200</v>
+      </c>
+      <c r="J46" s="35" t="n">
+        <v>200</v>
+      </c>
       <c r="K46" s="36"/>
       <c r="L46" s="36"/>
       <c r="M46" s="36"/>
@@ -4765,8 +5145,8 @@
       <c r="R46" s="36"/>
       <c r="S46" s="36"/>
       <c r="T46" s="36"/>
-      <c r="U46" s="37"/>
-      <c r="V46" s="36"/>
+      <c r="U46" s="36"/>
+      <c r="V46" s="37"/>
       <c r="W46" s="36"/>
       <c r="X46" s="36"/>
       <c r="Y46" s="36"/>
@@ -4783,8 +5163,8 @@
       <c r="AJ46" s="36"/>
       <c r="AK46" s="36"/>
       <c r="AL46" s="36"/>
-      <c r="AM46" s="37"/>
-      <c r="AN46" s="36"/>
+      <c r="AM46" s="36"/>
+      <c r="AN46" s="37"/>
       <c r="AO46" s="36"/>
       <c r="AP46" s="36"/>
       <c r="AQ46" s="36"/>
@@ -4793,8 +5173,8 @@
       <c r="AT46" s="36"/>
       <c r="AU46" s="36"/>
       <c r="AV46" s="36"/>
-      <c r="AW46" s="37"/>
-      <c r="AX46" s="36"/>
+      <c r="AW46" s="36"/>
+      <c r="AX46" s="37"/>
       <c r="AY46" s="36"/>
       <c r="AZ46" s="36"/>
       <c r="BA46" s="36"/>
@@ -4812,9 +5192,9 @@
       <c r="BM46" s="36"/>
       <c r="BN46" s="36"/>
       <c r="BO46" s="36"/>
-      <c r="BP46" s="37"/>
-      <c r="BQ46" s="38"/>
-      <c r="BR46" s="36"/>
+      <c r="BP46" s="36"/>
+      <c r="BQ46" s="37"/>
+      <c r="BR46" s="38"/>
       <c r="BS46" s="36"/>
       <c r="BT46" s="36"/>
       <c r="BU46" s="36"/>
@@ -4823,19 +5203,20 @@
       <c r="BX46" s="36"/>
       <c r="BY46" s="36"/>
       <c r="BZ46" s="36"/>
+      <c r="CA46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C47" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E47" s="34" t="n">
         <v>65</v>
@@ -4843,10 +5224,18 @@
       <c r="F47" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
+      <c r="G47" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="H47" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="I47" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="J47" s="35" t="n">
+        <v>120</v>
+      </c>
       <c r="K47" s="36"/>
       <c r="L47" s="36"/>
       <c r="M47" s="36"/>
@@ -4857,8 +5246,8 @@
       <c r="R47" s="36"/>
       <c r="S47" s="36"/>
       <c r="T47" s="36"/>
-      <c r="U47" s="37"/>
-      <c r="V47" s="36"/>
+      <c r="U47" s="36"/>
+      <c r="V47" s="37"/>
       <c r="W47" s="36"/>
       <c r="X47" s="36"/>
       <c r="Y47" s="36"/>
@@ -4875,8 +5264,8 @@
       <c r="AJ47" s="36"/>
       <c r="AK47" s="36"/>
       <c r="AL47" s="36"/>
-      <c r="AM47" s="37"/>
-      <c r="AN47" s="36"/>
+      <c r="AM47" s="36"/>
+      <c r="AN47" s="37"/>
       <c r="AO47" s="36"/>
       <c r="AP47" s="36"/>
       <c r="AQ47" s="36"/>
@@ -4885,8 +5274,8 @@
       <c r="AT47" s="36"/>
       <c r="AU47" s="36"/>
       <c r="AV47" s="36"/>
-      <c r="AW47" s="37"/>
-      <c r="AX47" s="36"/>
+      <c r="AW47" s="36"/>
+      <c r="AX47" s="37"/>
       <c r="AY47" s="36"/>
       <c r="AZ47" s="36"/>
       <c r="BA47" s="36"/>
@@ -4904,9 +5293,9 @@
       <c r="BM47" s="36"/>
       <c r="BN47" s="36"/>
       <c r="BO47" s="36"/>
-      <c r="BP47" s="37"/>
-      <c r="BQ47" s="38"/>
-      <c r="BR47" s="36"/>
+      <c r="BP47" s="36"/>
+      <c r="BQ47" s="37"/>
+      <c r="BR47" s="38"/>
       <c r="BS47" s="36"/>
       <c r="BT47" s="36"/>
       <c r="BU47" s="36"/>
@@ -4915,19 +5304,20 @@
       <c r="BX47" s="36"/>
       <c r="BY47" s="36"/>
       <c r="BZ47" s="36"/>
+      <c r="CA47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="32" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C48" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E48" s="34" t="n">
         <v>68</v>
@@ -4935,10 +5325,18 @@
       <c r="F48" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
+      <c r="G48" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="I48" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J48" s="35" t="n">
+        <v>20</v>
+      </c>
       <c r="K48" s="36"/>
       <c r="L48" s="36"/>
       <c r="M48" s="36"/>
@@ -4949,8 +5347,8 @@
       <c r="R48" s="36"/>
       <c r="S48" s="36"/>
       <c r="T48" s="36"/>
-      <c r="U48" s="37"/>
-      <c r="V48" s="36"/>
+      <c r="U48" s="36"/>
+      <c r="V48" s="37"/>
       <c r="W48" s="36"/>
       <c r="X48" s="36"/>
       <c r="Y48" s="36"/>
@@ -4967,8 +5365,8 @@
       <c r="AJ48" s="36"/>
       <c r="AK48" s="36"/>
       <c r="AL48" s="36"/>
-      <c r="AM48" s="37"/>
-      <c r="AN48" s="36"/>
+      <c r="AM48" s="36"/>
+      <c r="AN48" s="37"/>
       <c r="AO48" s="36"/>
       <c r="AP48" s="36"/>
       <c r="AQ48" s="36"/>
@@ -4977,8 +5375,8 @@
       <c r="AT48" s="36"/>
       <c r="AU48" s="36"/>
       <c r="AV48" s="36"/>
-      <c r="AW48" s="37"/>
-      <c r="AX48" s="36"/>
+      <c r="AW48" s="36"/>
+      <c r="AX48" s="37"/>
       <c r="AY48" s="36"/>
       <c r="AZ48" s="36"/>
       <c r="BA48" s="36"/>
@@ -4996,9 +5394,9 @@
       <c r="BM48" s="36"/>
       <c r="BN48" s="36"/>
       <c r="BO48" s="36"/>
-      <c r="BP48" s="37"/>
-      <c r="BQ48" s="38"/>
-      <c r="BR48" s="36"/>
+      <c r="BP48" s="36"/>
+      <c r="BQ48" s="37"/>
+      <c r="BR48" s="38"/>
       <c r="BS48" s="36"/>
       <c r="BT48" s="36"/>
       <c r="BU48" s="36"/>
@@ -5007,19 +5405,20 @@
       <c r="BX48" s="36"/>
       <c r="BY48" s="36"/>
       <c r="BZ48" s="36"/>
+      <c r="CA48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="32" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C49" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E49" s="34" t="n">
         <v>72</v>
@@ -5027,10 +5426,18 @@
       <c r="F49" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
+      <c r="G49" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="H49" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="I49" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="J49" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="K49" s="36"/>
       <c r="L49" s="36"/>
       <c r="M49" s="36"/>
@@ -5041,8 +5448,8 @@
       <c r="R49" s="36"/>
       <c r="S49" s="36"/>
       <c r="T49" s="36"/>
-      <c r="U49" s="37"/>
-      <c r="V49" s="36"/>
+      <c r="U49" s="36"/>
+      <c r="V49" s="37"/>
       <c r="W49" s="36"/>
       <c r="X49" s="36"/>
       <c r="Y49" s="36"/>
@@ -5059,8 +5466,8 @@
       <c r="AJ49" s="36"/>
       <c r="AK49" s="36"/>
       <c r="AL49" s="36"/>
-      <c r="AM49" s="37"/>
-      <c r="AN49" s="36"/>
+      <c r="AM49" s="36"/>
+      <c r="AN49" s="37"/>
       <c r="AO49" s="36"/>
       <c r="AP49" s="36"/>
       <c r="AQ49" s="36"/>
@@ -5069,8 +5476,8 @@
       <c r="AT49" s="36"/>
       <c r="AU49" s="36"/>
       <c r="AV49" s="36"/>
-      <c r="AW49" s="37"/>
-      <c r="AX49" s="36"/>
+      <c r="AW49" s="36"/>
+      <c r="AX49" s="37"/>
       <c r="AY49" s="36"/>
       <c r="AZ49" s="36"/>
       <c r="BA49" s="36"/>
@@ -5088,9 +5495,9 @@
       <c r="BM49" s="36"/>
       <c r="BN49" s="36"/>
       <c r="BO49" s="36"/>
-      <c r="BP49" s="37"/>
-      <c r="BQ49" s="38"/>
-      <c r="BR49" s="36"/>
+      <c r="BP49" s="36"/>
+      <c r="BQ49" s="37"/>
+      <c r="BR49" s="38"/>
       <c r="BS49" s="36"/>
       <c r="BT49" s="36"/>
       <c r="BU49" s="36"/>
@@ -5099,19 +5506,20 @@
       <c r="BX49" s="36"/>
       <c r="BY49" s="36"/>
       <c r="BZ49" s="36"/>
+      <c r="CA49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="32" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C50" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E50" s="34" t="n">
         <v>72</v>
@@ -5119,10 +5527,18 @@
       <c r="F50" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="G50" s="36"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="36"/>
+      <c r="G50" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="H50" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="I50" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="J50" s="35" t="n">
+        <v>150</v>
+      </c>
       <c r="K50" s="36"/>
       <c r="L50" s="36"/>
       <c r="M50" s="36"/>
@@ -5133,8 +5549,8 @@
       <c r="R50" s="36"/>
       <c r="S50" s="36"/>
       <c r="T50" s="36"/>
-      <c r="U50" s="37"/>
-      <c r="V50" s="36"/>
+      <c r="U50" s="36"/>
+      <c r="V50" s="37"/>
       <c r="W50" s="36"/>
       <c r="X50" s="36"/>
       <c r="Y50" s="36"/>
@@ -5151,8 +5567,8 @@
       <c r="AJ50" s="36"/>
       <c r="AK50" s="36"/>
       <c r="AL50" s="36"/>
-      <c r="AM50" s="37"/>
-      <c r="AN50" s="36"/>
+      <c r="AM50" s="36"/>
+      <c r="AN50" s="37"/>
       <c r="AO50" s="36"/>
       <c r="AP50" s="36"/>
       <c r="AQ50" s="36"/>
@@ -5161,8 +5577,8 @@
       <c r="AT50" s="36"/>
       <c r="AU50" s="36"/>
       <c r="AV50" s="36"/>
-      <c r="AW50" s="37"/>
-      <c r="AX50" s="36"/>
+      <c r="AW50" s="36"/>
+      <c r="AX50" s="37"/>
       <c r="AY50" s="36"/>
       <c r="AZ50" s="36"/>
       <c r="BA50" s="36"/>
@@ -5180,9 +5596,9 @@
       <c r="BM50" s="36"/>
       <c r="BN50" s="36"/>
       <c r="BO50" s="36"/>
-      <c r="BP50" s="37"/>
-      <c r="BQ50" s="38"/>
-      <c r="BR50" s="36"/>
+      <c r="BP50" s="36"/>
+      <c r="BQ50" s="37"/>
+      <c r="BR50" s="38"/>
       <c r="BS50" s="36"/>
       <c r="BT50" s="36"/>
       <c r="BU50" s="36"/>
@@ -5191,30 +5607,39 @@
       <c r="BX50" s="36"/>
       <c r="BY50" s="36"/>
       <c r="BZ50" s="36"/>
+      <c r="CA50" s="36"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="32" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C51" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F51" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="G51" s="36"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="36"/>
+      <c r="G51" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="H51" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="I51" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="J51" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="K51" s="36"/>
       <c r="L51" s="36"/>
       <c r="M51" s="36"/>
@@ -5225,8 +5650,8 @@
       <c r="R51" s="36"/>
       <c r="S51" s="36"/>
       <c r="T51" s="36"/>
-      <c r="U51" s="37"/>
-      <c r="V51" s="36"/>
+      <c r="U51" s="36"/>
+      <c r="V51" s="37"/>
       <c r="W51" s="36"/>
       <c r="X51" s="36"/>
       <c r="Y51" s="36"/>
@@ -5243,8 +5668,8 @@
       <c r="AJ51" s="36"/>
       <c r="AK51" s="36"/>
       <c r="AL51" s="36"/>
-      <c r="AM51" s="37"/>
-      <c r="AN51" s="36"/>
+      <c r="AM51" s="36"/>
+      <c r="AN51" s="37"/>
       <c r="AO51" s="36"/>
       <c r="AP51" s="36"/>
       <c r="AQ51" s="36"/>
@@ -5253,8 +5678,8 @@
       <c r="AT51" s="36"/>
       <c r="AU51" s="36"/>
       <c r="AV51" s="36"/>
-      <c r="AW51" s="37"/>
-      <c r="AX51" s="36"/>
+      <c r="AW51" s="36"/>
+      <c r="AX51" s="37"/>
       <c r="AY51" s="36"/>
       <c r="AZ51" s="36"/>
       <c r="BA51" s="36"/>
@@ -5272,9 +5697,9 @@
       <c r="BM51" s="36"/>
       <c r="BN51" s="36"/>
       <c r="BO51" s="36"/>
-      <c r="BP51" s="37"/>
-      <c r="BQ51" s="38"/>
-      <c r="BR51" s="36"/>
+      <c r="BP51" s="36"/>
+      <c r="BQ51" s="37"/>
+      <c r="BR51" s="38"/>
       <c r="BS51" s="36"/>
       <c r="BT51" s="36"/>
       <c r="BU51" s="36"/>
@@ -5283,30 +5708,39 @@
       <c r="BX51" s="36"/>
       <c r="BY51" s="36"/>
       <c r="BZ51" s="36"/>
+      <c r="CA51" s="36"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="32" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C52" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F52" s="35" t="n">
         <v>72</v>
       </c>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="36"/>
+      <c r="G52" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="H52" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="I52" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="J52" s="35" t="n">
+        <v>72</v>
+      </c>
       <c r="K52" s="36"/>
       <c r="L52" s="36"/>
       <c r="M52" s="36"/>
@@ -5317,8 +5751,8 @@
       <c r="R52" s="36"/>
       <c r="S52" s="36"/>
       <c r="T52" s="36"/>
-      <c r="U52" s="37"/>
-      <c r="V52" s="36"/>
+      <c r="U52" s="36"/>
+      <c r="V52" s="37"/>
       <c r="W52" s="36"/>
       <c r="X52" s="36"/>
       <c r="Y52" s="36"/>
@@ -5335,8 +5769,8 @@
       <c r="AJ52" s="36"/>
       <c r="AK52" s="36"/>
       <c r="AL52" s="36"/>
-      <c r="AM52" s="37"/>
-      <c r="AN52" s="36"/>
+      <c r="AM52" s="36"/>
+      <c r="AN52" s="37"/>
       <c r="AO52" s="36"/>
       <c r="AP52" s="36"/>
       <c r="AQ52" s="36"/>
@@ -5345,8 +5779,8 @@
       <c r="AT52" s="36"/>
       <c r="AU52" s="36"/>
       <c r="AV52" s="36"/>
-      <c r="AW52" s="37"/>
-      <c r="AX52" s="36"/>
+      <c r="AW52" s="36"/>
+      <c r="AX52" s="37"/>
       <c r="AY52" s="36"/>
       <c r="AZ52" s="36"/>
       <c r="BA52" s="36"/>
@@ -5364,9 +5798,9 @@
       <c r="BM52" s="36"/>
       <c r="BN52" s="36"/>
       <c r="BO52" s="36"/>
-      <c r="BP52" s="37"/>
-      <c r="BQ52" s="38"/>
-      <c r="BR52" s="36"/>
+      <c r="BP52" s="36"/>
+      <c r="BQ52" s="37"/>
+      <c r="BR52" s="38"/>
       <c r="BS52" s="36"/>
       <c r="BT52" s="36"/>
       <c r="BU52" s="36"/>
@@ -5375,30 +5809,39 @@
       <c r="BX52" s="36"/>
       <c r="BY52" s="36"/>
       <c r="BZ52" s="36"/>
+      <c r="CA52" s="36"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="32" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C53" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F53" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
+      <c r="G53" s="35" t="n">
+        <v>400</v>
+      </c>
+      <c r="H53" s="35" t="n">
+        <v>400</v>
+      </c>
+      <c r="I53" s="35" t="n">
+        <v>400</v>
+      </c>
+      <c r="J53" s="35" t="n">
+        <v>400</v>
+      </c>
       <c r="K53" s="36"/>
       <c r="L53" s="36"/>
       <c r="M53" s="36"/>
@@ -5409,8 +5852,8 @@
       <c r="R53" s="36"/>
       <c r="S53" s="36"/>
       <c r="T53" s="36"/>
-      <c r="U53" s="37"/>
-      <c r="V53" s="36"/>
+      <c r="U53" s="36"/>
+      <c r="V53" s="37"/>
       <c r="W53" s="36"/>
       <c r="X53" s="36"/>
       <c r="Y53" s="36"/>
@@ -5427,8 +5870,8 @@
       <c r="AJ53" s="36"/>
       <c r="AK53" s="36"/>
       <c r="AL53" s="36"/>
-      <c r="AM53" s="37"/>
-      <c r="AN53" s="36"/>
+      <c r="AM53" s="36"/>
+      <c r="AN53" s="37"/>
       <c r="AO53" s="36"/>
       <c r="AP53" s="36"/>
       <c r="AQ53" s="36"/>
@@ -5437,8 +5880,8 @@
       <c r="AT53" s="36"/>
       <c r="AU53" s="36"/>
       <c r="AV53" s="36"/>
-      <c r="AW53" s="37"/>
-      <c r="AX53" s="36"/>
+      <c r="AW53" s="36"/>
+      <c r="AX53" s="37"/>
       <c r="AY53" s="36"/>
       <c r="AZ53" s="36"/>
       <c r="BA53" s="36"/>
@@ -5456,9 +5899,9 @@
       <c r="BM53" s="36"/>
       <c r="BN53" s="36"/>
       <c r="BO53" s="36"/>
-      <c r="BP53" s="37"/>
-      <c r="BQ53" s="38"/>
-      <c r="BR53" s="36"/>
+      <c r="BP53" s="36"/>
+      <c r="BQ53" s="37"/>
+      <c r="BR53" s="38"/>
       <c r="BS53" s="36"/>
       <c r="BT53" s="36"/>
       <c r="BU53" s="36"/>
@@ -5467,30 +5910,39 @@
       <c r="BX53" s="36"/>
       <c r="BY53" s="36"/>
       <c r="BZ53" s="36"/>
+      <c r="CA53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="32" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C54" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36"/>
+        <v>55</v>
+      </c>
+      <c r="G54" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="H54" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="I54" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="J54" s="35" t="s">
+        <v>55</v>
+      </c>
       <c r="K54" s="36"/>
       <c r="L54" s="36"/>
       <c r="M54" s="36"/>
@@ -5501,8 +5953,8 @@
       <c r="R54" s="36"/>
       <c r="S54" s="36"/>
       <c r="T54" s="36"/>
-      <c r="U54" s="37"/>
-      <c r="V54" s="36"/>
+      <c r="U54" s="36"/>
+      <c r="V54" s="37"/>
       <c r="W54" s="36"/>
       <c r="X54" s="36"/>
       <c r="Y54" s="36"/>
@@ -5519,8 +5971,8 @@
       <c r="AJ54" s="36"/>
       <c r="AK54" s="36"/>
       <c r="AL54" s="36"/>
-      <c r="AM54" s="37"/>
-      <c r="AN54" s="36"/>
+      <c r="AM54" s="36"/>
+      <c r="AN54" s="37"/>
       <c r="AO54" s="36"/>
       <c r="AP54" s="36"/>
       <c r="AQ54" s="36"/>
@@ -5529,8 +5981,8 @@
       <c r="AT54" s="36"/>
       <c r="AU54" s="36"/>
       <c r="AV54" s="36"/>
-      <c r="AW54" s="37"/>
-      <c r="AX54" s="36"/>
+      <c r="AW54" s="36"/>
+      <c r="AX54" s="37"/>
       <c r="AY54" s="36"/>
       <c r="AZ54" s="36"/>
       <c r="BA54" s="36"/>
@@ -5548,9 +6000,9 @@
       <c r="BM54" s="36"/>
       <c r="BN54" s="36"/>
       <c r="BO54" s="36"/>
-      <c r="BP54" s="37"/>
-      <c r="BQ54" s="38"/>
-      <c r="BR54" s="36"/>
+      <c r="BP54" s="36"/>
+      <c r="BQ54" s="37"/>
+      <c r="BR54" s="38"/>
       <c r="BS54" s="36"/>
       <c r="BT54" s="36"/>
       <c r="BU54" s="36"/>
@@ -5559,30 +6011,39 @@
       <c r="BX54" s="36"/>
       <c r="BY54" s="36"/>
       <c r="BZ54" s="36"/>
+      <c r="CA54" s="36"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="32" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C55" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E55" s="34" t="n">
         <v>72</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="G55" s="36"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="36"/>
-      <c r="J55" s="36"/>
+        <v>59</v>
+      </c>
+      <c r="G55" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="H55" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I55" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="J55" s="35" t="s">
+        <v>59</v>
+      </c>
       <c r="K55" s="36"/>
       <c r="L55" s="36"/>
       <c r="M55" s="36"/>
@@ -5593,8 +6054,8 @@
       <c r="R55" s="36"/>
       <c r="S55" s="36"/>
       <c r="T55" s="36"/>
-      <c r="U55" s="37"/>
-      <c r="V55" s="36"/>
+      <c r="U55" s="36"/>
+      <c r="V55" s="37"/>
       <c r="W55" s="36"/>
       <c r="X55" s="36"/>
       <c r="Y55" s="36"/>
@@ -5611,8 +6072,8 @@
       <c r="AJ55" s="36"/>
       <c r="AK55" s="36"/>
       <c r="AL55" s="36"/>
-      <c r="AM55" s="37"/>
-      <c r="AN55" s="36"/>
+      <c r="AM55" s="36"/>
+      <c r="AN55" s="37"/>
       <c r="AO55" s="36"/>
       <c r="AP55" s="36"/>
       <c r="AQ55" s="36"/>
@@ -5621,8 +6082,8 @@
       <c r="AT55" s="36"/>
       <c r="AU55" s="36"/>
       <c r="AV55" s="36"/>
-      <c r="AW55" s="37"/>
-      <c r="AX55" s="36"/>
+      <c r="AW55" s="36"/>
+      <c r="AX55" s="37"/>
       <c r="AY55" s="36"/>
       <c r="AZ55" s="36"/>
       <c r="BA55" s="36"/>
@@ -5640,9 +6101,9 @@
       <c r="BM55" s="36"/>
       <c r="BN55" s="36"/>
       <c r="BO55" s="36"/>
-      <c r="BP55" s="37"/>
-      <c r="BQ55" s="38"/>
-      <c r="BR55" s="36"/>
+      <c r="BP55" s="36"/>
+      <c r="BQ55" s="37"/>
+      <c r="BR55" s="38"/>
       <c r="BS55" s="36"/>
       <c r="BT55" s="36"/>
       <c r="BU55" s="36"/>
@@ -5651,19 +6112,20 @@
       <c r="BX55" s="36"/>
       <c r="BY55" s="36"/>
       <c r="BZ55" s="36"/>
+      <c r="CA55" s="36"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C56" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E56" s="34" t="n">
         <v>720</v>
@@ -5671,10 +6133,18 @@
       <c r="F56" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
+      <c r="G56" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K56" s="36"/>
       <c r="L56" s="36"/>
       <c r="M56" s="36"/>
@@ -5685,8 +6155,8 @@
       <c r="R56" s="36"/>
       <c r="S56" s="36"/>
       <c r="T56" s="36"/>
-      <c r="U56" s="37"/>
-      <c r="V56" s="36"/>
+      <c r="U56" s="36"/>
+      <c r="V56" s="37"/>
       <c r="W56" s="36"/>
       <c r="X56" s="36"/>
       <c r="Y56" s="36"/>
@@ -5703,8 +6173,8 @@
       <c r="AJ56" s="36"/>
       <c r="AK56" s="36"/>
       <c r="AL56" s="36"/>
-      <c r="AM56" s="37"/>
-      <c r="AN56" s="36"/>
+      <c r="AM56" s="36"/>
+      <c r="AN56" s="37"/>
       <c r="AO56" s="36"/>
       <c r="AP56" s="36"/>
       <c r="AQ56" s="36"/>
@@ -5713,8 +6183,8 @@
       <c r="AT56" s="36"/>
       <c r="AU56" s="36"/>
       <c r="AV56" s="36"/>
-      <c r="AW56" s="37"/>
-      <c r="AX56" s="36"/>
+      <c r="AW56" s="36"/>
+      <c r="AX56" s="37"/>
       <c r="AY56" s="36"/>
       <c r="AZ56" s="36"/>
       <c r="BA56" s="36"/>
@@ -5732,9 +6202,9 @@
       <c r="BM56" s="36"/>
       <c r="BN56" s="36"/>
       <c r="BO56" s="36"/>
-      <c r="BP56" s="37"/>
-      <c r="BQ56" s="38"/>
-      <c r="BR56" s="36"/>
+      <c r="BP56" s="36"/>
+      <c r="BQ56" s="37"/>
+      <c r="BR56" s="38"/>
       <c r="BS56" s="36"/>
       <c r="BT56" s="36"/>
       <c r="BU56" s="36"/>
@@ -5743,19 +6213,20 @@
       <c r="BX56" s="36"/>
       <c r="BY56" s="36"/>
       <c r="BZ56" s="36"/>
+      <c r="CA56" s="36"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="32" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C57" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E57" s="34" t="n">
         <v>48</v>
@@ -5763,10 +6234,18 @@
       <c r="F57" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G57" s="36"/>
-      <c r="H57" s="36"/>
-      <c r="I57" s="36"/>
-      <c r="J57" s="36"/>
+      <c r="G57" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K57" s="36"/>
       <c r="L57" s="36"/>
       <c r="M57" s="36"/>
@@ -5777,8 +6256,8 @@
       <c r="R57" s="36"/>
       <c r="S57" s="36"/>
       <c r="T57" s="36"/>
-      <c r="U57" s="37"/>
-      <c r="V57" s="36"/>
+      <c r="U57" s="36"/>
+      <c r="V57" s="37"/>
       <c r="W57" s="36"/>
       <c r="X57" s="36"/>
       <c r="Y57" s="36"/>
@@ -5795,8 +6274,8 @@
       <c r="AJ57" s="36"/>
       <c r="AK57" s="36"/>
       <c r="AL57" s="36"/>
-      <c r="AM57" s="37"/>
-      <c r="AN57" s="36"/>
+      <c r="AM57" s="36"/>
+      <c r="AN57" s="37"/>
       <c r="AO57" s="36"/>
       <c r="AP57" s="36"/>
       <c r="AQ57" s="36"/>
@@ -5805,8 +6284,8 @@
       <c r="AT57" s="36"/>
       <c r="AU57" s="36"/>
       <c r="AV57" s="36"/>
-      <c r="AW57" s="37"/>
-      <c r="AX57" s="36"/>
+      <c r="AW57" s="36"/>
+      <c r="AX57" s="37"/>
       <c r="AY57" s="36"/>
       <c r="AZ57" s="36"/>
       <c r="BA57" s="36"/>
@@ -5824,9 +6303,9 @@
       <c r="BM57" s="36"/>
       <c r="BN57" s="36"/>
       <c r="BO57" s="36"/>
-      <c r="BP57" s="37"/>
-      <c r="BQ57" s="38"/>
-      <c r="BR57" s="36"/>
+      <c r="BP57" s="36"/>
+      <c r="BQ57" s="37"/>
+      <c r="BR57" s="38"/>
       <c r="BS57" s="36"/>
       <c r="BT57" s="36"/>
       <c r="BU57" s="36"/>
@@ -5835,19 +6314,20 @@
       <c r="BX57" s="36"/>
       <c r="BY57" s="36"/>
       <c r="BZ57" s="36"/>
+      <c r="CA57" s="36"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="32" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C58" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>72</v>
@@ -5855,10 +6335,18 @@
       <c r="F58" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="36"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="36"/>
+      <c r="G58" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" s="36"/>
       <c r="L58" s="36"/>
       <c r="M58" s="36"/>
@@ -5869,8 +6357,8 @@
       <c r="R58" s="36"/>
       <c r="S58" s="36"/>
       <c r="T58" s="36"/>
-      <c r="U58" s="37"/>
-      <c r="V58" s="36"/>
+      <c r="U58" s="36"/>
+      <c r="V58" s="37"/>
       <c r="W58" s="36"/>
       <c r="X58" s="36"/>
       <c r="Y58" s="36"/>
@@ -5887,8 +6375,8 @@
       <c r="AJ58" s="36"/>
       <c r="AK58" s="36"/>
       <c r="AL58" s="36"/>
-      <c r="AM58" s="37"/>
-      <c r="AN58" s="36"/>
+      <c r="AM58" s="36"/>
+      <c r="AN58" s="37"/>
       <c r="AO58" s="36"/>
       <c r="AP58" s="36"/>
       <c r="AQ58" s="36"/>
@@ -5897,8 +6385,8 @@
       <c r="AT58" s="36"/>
       <c r="AU58" s="36"/>
       <c r="AV58" s="36"/>
-      <c r="AW58" s="37"/>
-      <c r="AX58" s="36"/>
+      <c r="AW58" s="36"/>
+      <c r="AX58" s="37"/>
       <c r="AY58" s="36"/>
       <c r="AZ58" s="36"/>
       <c r="BA58" s="36"/>
@@ -5916,9 +6404,9 @@
       <c r="BM58" s="36"/>
       <c r="BN58" s="36"/>
       <c r="BO58" s="36"/>
-      <c r="BP58" s="37"/>
-      <c r="BQ58" s="38"/>
-      <c r="BR58" s="36"/>
+      <c r="BP58" s="36"/>
+      <c r="BQ58" s="37"/>
+      <c r="BR58" s="38"/>
       <c r="BS58" s="36"/>
       <c r="BT58" s="36"/>
       <c r="BU58" s="36"/>
@@ -5927,19 +6415,20 @@
       <c r="BX58" s="36"/>
       <c r="BY58" s="36"/>
       <c r="BZ58" s="36"/>
+      <c r="CA58" s="36"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C59" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E59" s="34" t="n">
         <v>84</v>
@@ -5947,10 +6436,18 @@
       <c r="F59" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="36"/>
+      <c r="G59" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" s="36"/>
       <c r="L59" s="36"/>
       <c r="M59" s="36"/>
@@ -5961,8 +6458,8 @@
       <c r="R59" s="36"/>
       <c r="S59" s="36"/>
       <c r="T59" s="36"/>
-      <c r="U59" s="37"/>
-      <c r="V59" s="36"/>
+      <c r="U59" s="36"/>
+      <c r="V59" s="37"/>
       <c r="W59" s="36"/>
       <c r="X59" s="36"/>
       <c r="Y59" s="36"/>
@@ -5979,8 +6476,8 @@
       <c r="AJ59" s="36"/>
       <c r="AK59" s="36"/>
       <c r="AL59" s="36"/>
-      <c r="AM59" s="37"/>
-      <c r="AN59" s="36"/>
+      <c r="AM59" s="36"/>
+      <c r="AN59" s="37"/>
       <c r="AO59" s="36"/>
       <c r="AP59" s="36"/>
       <c r="AQ59" s="36"/>
@@ -5989,8 +6486,8 @@
       <c r="AT59" s="36"/>
       <c r="AU59" s="36"/>
       <c r="AV59" s="36"/>
-      <c r="AW59" s="37"/>
-      <c r="AX59" s="36"/>
+      <c r="AW59" s="36"/>
+      <c r="AX59" s="37"/>
       <c r="AY59" s="36"/>
       <c r="AZ59" s="36"/>
       <c r="BA59" s="36"/>
@@ -6008,9 +6505,9 @@
       <c r="BM59" s="36"/>
       <c r="BN59" s="36"/>
       <c r="BO59" s="36"/>
-      <c r="BP59" s="37"/>
-      <c r="BQ59" s="38"/>
-      <c r="BR59" s="36"/>
+      <c r="BP59" s="36"/>
+      <c r="BQ59" s="37"/>
+      <c r="BR59" s="38"/>
       <c r="BS59" s="36"/>
       <c r="BT59" s="36"/>
       <c r="BU59" s="36"/>
@@ -6019,30 +6516,39 @@
       <c r="BX59" s="36"/>
       <c r="BY59" s="36"/>
       <c r="BZ59" s="36"/>
+      <c r="CA59" s="36"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="32" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C60" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F60" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="G60" s="36"/>
-      <c r="H60" s="36"/>
-      <c r="I60" s="36"/>
-      <c r="J60" s="36"/>
+      <c r="G60" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="H60" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="I60" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="J60" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="K60" s="36"/>
       <c r="L60" s="36"/>
       <c r="M60" s="36"/>
@@ -6053,8 +6559,8 @@
       <c r="R60" s="36"/>
       <c r="S60" s="36"/>
       <c r="T60" s="36"/>
-      <c r="U60" s="37"/>
-      <c r="V60" s="36"/>
+      <c r="U60" s="36"/>
+      <c r="V60" s="37"/>
       <c r="W60" s="36"/>
       <c r="X60" s="36"/>
       <c r="Y60" s="36"/>
@@ -6071,8 +6577,8 @@
       <c r="AJ60" s="36"/>
       <c r="AK60" s="36"/>
       <c r="AL60" s="36"/>
-      <c r="AM60" s="37"/>
-      <c r="AN60" s="36"/>
+      <c r="AM60" s="36"/>
+      <c r="AN60" s="37"/>
       <c r="AO60" s="36"/>
       <c r="AP60" s="36"/>
       <c r="AQ60" s="36"/>
@@ -6081,8 +6587,8 @@
       <c r="AT60" s="36"/>
       <c r="AU60" s="36"/>
       <c r="AV60" s="36"/>
-      <c r="AW60" s="37"/>
-      <c r="AX60" s="36"/>
+      <c r="AW60" s="36"/>
+      <c r="AX60" s="37"/>
       <c r="AY60" s="36"/>
       <c r="AZ60" s="36"/>
       <c r="BA60" s="36"/>
@@ -6100,9 +6606,9 @@
       <c r="BM60" s="36"/>
       <c r="BN60" s="36"/>
       <c r="BO60" s="36"/>
-      <c r="BP60" s="37"/>
-      <c r="BQ60" s="38"/>
-      <c r="BR60" s="36"/>
+      <c r="BP60" s="36"/>
+      <c r="BQ60" s="37"/>
+      <c r="BR60" s="38"/>
       <c r="BS60" s="36"/>
       <c r="BT60" s="36"/>
       <c r="BU60" s="36"/>
@@ -6111,30 +6617,39 @@
       <c r="BX60" s="36"/>
       <c r="BY60" s="36"/>
       <c r="BZ60" s="36"/>
+      <c r="CA60" s="36"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C61" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F61" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="G61" s="36"/>
-      <c r="H61" s="36"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="36"/>
+      <c r="G61" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="H61" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="I61" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="J61" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="K61" s="36"/>
       <c r="L61" s="36"/>
       <c r="M61" s="36"/>
@@ -6145,8 +6660,8 @@
       <c r="R61" s="36"/>
       <c r="S61" s="36"/>
       <c r="T61" s="36"/>
-      <c r="U61" s="37"/>
-      <c r="V61" s="36"/>
+      <c r="U61" s="36"/>
+      <c r="V61" s="37"/>
       <c r="W61" s="36"/>
       <c r="X61" s="36"/>
       <c r="Y61" s="36"/>
@@ -6163,8 +6678,8 @@
       <c r="AJ61" s="36"/>
       <c r="AK61" s="36"/>
       <c r="AL61" s="36"/>
-      <c r="AM61" s="37"/>
-      <c r="AN61" s="36"/>
+      <c r="AM61" s="36"/>
+      <c r="AN61" s="37"/>
       <c r="AO61" s="36"/>
       <c r="AP61" s="36"/>
       <c r="AQ61" s="36"/>
@@ -6173,8 +6688,8 @@
       <c r="AT61" s="36"/>
       <c r="AU61" s="36"/>
       <c r="AV61" s="36"/>
-      <c r="AW61" s="37"/>
-      <c r="AX61" s="36"/>
+      <c r="AW61" s="36"/>
+      <c r="AX61" s="37"/>
       <c r="AY61" s="36"/>
       <c r="AZ61" s="36"/>
       <c r="BA61" s="36"/>
@@ -6192,9 +6707,9 @@
       <c r="BM61" s="36"/>
       <c r="BN61" s="36"/>
       <c r="BO61" s="36"/>
-      <c r="BP61" s="37"/>
-      <c r="BQ61" s="38"/>
-      <c r="BR61" s="36"/>
+      <c r="BP61" s="36"/>
+      <c r="BQ61" s="37"/>
+      <c r="BR61" s="38"/>
       <c r="BS61" s="36"/>
       <c r="BT61" s="36"/>
       <c r="BU61" s="36"/>
@@ -6203,14 +6718,12 @@
       <c r="BX61" s="36"/>
       <c r="BY61" s="36"/>
       <c r="BZ61" s="36"/>
+      <c r="CA61" s="36"/>
     </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="G8:ZY33 G39:ZY61">
+  <conditionalFormatting sqref="K8:ZZ33 K39:ZZ61">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>#ref!&lt;&gt;G8</formula>
+      <formula>#ref!&lt;&gt;K8</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
+++ b/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="130">
   <si>
     <t xml:space="preserve">Dummy Test</t>
   </si>
@@ -203,6 +203,9 @@
     <t xml:space="preserve">7</t>
   </si>
   <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -449,6 +452,9 @@
     <t xml:space="preserve">ts_y1</t>
   </si>
   <si>
+    <t xml:space="preserve">ts_y11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Variable Value</t>
   </si>
   <si>
@@ -461,7 +467,7 @@
     <t xml:space="preserve">&lt;=71</t>
   </si>
   <si>
-    <t xml:space="preserve">ts_y11</t>
+    <t xml:space="preserve">&gt;=70</t>
   </si>
   <si>
     <t xml:space="preserve">Expected Outputs</t>
@@ -1315,7 +1321,9 @@
       <c r="J6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="19"/>
+      <c r="K6" s="18" t="s">
+        <v>4</v>
+      </c>
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
@@ -1418,7 +1426,9 @@
       <c r="J7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="26"/>
+      <c r="K7" s="25" t="s">
+        <v>12</v>
+      </c>
       <c r="L7" s="26"/>
       <c r="M7" s="26"/>
       <c r="N7" s="26"/>
@@ -1490,10 +1500,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="34" t="n">
@@ -1517,7 +1527,9 @@
       <c r="J8" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="K8" s="36"/>
+      <c r="K8" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="L8" s="36"/>
       <c r="M8" s="36"/>
       <c r="N8" s="36"/>
@@ -1589,10 +1601,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="35" t="n">
@@ -1616,7 +1628,9 @@
       <c r="J9" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="K9" s="36"/>
+      <c r="K9" s="35" t="n">
+        <v>75</v>
+      </c>
       <c r="L9" s="36"/>
       <c r="M9" s="36"/>
       <c r="N9" s="36"/>
@@ -1688,10 +1702,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="39"/>
       <c r="D10" s="35" t="n">
@@ -1715,7 +1729,9 @@
       <c r="J10" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="K10" s="36"/>
+      <c r="K10" s="35" t="n">
+        <v>60</v>
+      </c>
       <c r="L10" s="36"/>
       <c r="M10" s="36"/>
       <c r="N10" s="36"/>
@@ -1787,10 +1803,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="39"/>
       <c r="D11" s="35" t="n">
@@ -1814,7 +1830,9 @@
       <c r="J11" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="K11" s="36"/>
+      <c r="K11" s="35" t="n">
+        <v>90</v>
+      </c>
       <c r="L11" s="36"/>
       <c r="M11" s="36"/>
       <c r="N11" s="36"/>
@@ -1886,10 +1904,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="33"/>
       <c r="D12" s="35" t="n">
@@ -1913,7 +1931,9 @@
       <c r="J12" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="K12" s="36"/>
+      <c r="K12" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="L12" s="36"/>
       <c r="M12" s="36"/>
       <c r="N12" s="36"/>
@@ -1985,17 +2005,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="35" t="n">
         <v>500</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13" s="35" t="n">
         <v>500</v>
@@ -2012,7 +2032,9 @@
       <c r="J13" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="K13" s="36"/>
+      <c r="K13" s="35" t="n">
+        <v>500</v>
+      </c>
       <c r="L13" s="36"/>
       <c r="M13" s="36"/>
       <c r="N13" s="36"/>
@@ -2084,10 +2106,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="35" t="n">
@@ -2111,7 +2133,9 @@
       <c r="J14" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="K14" s="36"/>
+      <c r="K14" s="35" t="n">
+        <v>100</v>
+      </c>
       <c r="L14" s="36"/>
       <c r="M14" s="36"/>
       <c r="N14" s="36"/>
@@ -2183,17 +2207,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="35" t="n">
         <v>200</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" s="35" t="n">
         <v>200</v>
@@ -2210,7 +2234,9 @@
       <c r="J15" s="35" t="n">
         <v>200</v>
       </c>
-      <c r="K15" s="36"/>
+      <c r="K15" s="35" t="n">
+        <v>200</v>
+      </c>
       <c r="L15" s="36"/>
       <c r="M15" s="36"/>
       <c r="N15" s="36"/>
@@ -2282,17 +2308,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="35" t="n">
         <v>120</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" s="35" t="n">
         <v>120</v>
@@ -2309,7 +2335,9 @@
       <c r="J16" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="K16" s="36"/>
+      <c r="K16" s="35" t="n">
+        <v>120</v>
+      </c>
       <c r="L16" s="36"/>
       <c r="M16" s="36"/>
       <c r="N16" s="36"/>
@@ -2381,17 +2409,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="35" t="n">
         <v>20</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>20</v>
@@ -2408,7 +2436,9 @@
       <c r="J17" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="K17" s="36"/>
+      <c r="K17" s="35" t="n">
+        <v>20</v>
+      </c>
       <c r="L17" s="36"/>
       <c r="M17" s="36"/>
       <c r="N17" s="36"/>
@@ -2480,34 +2510,36 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="39"/>
       <c r="D18" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="35" t="s">
-        <v>38</v>
-      </c>
       <c r="G18" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="K18" s="36"/>
       <c r="L18" s="36"/>
       <c r="M18" s="36"/>
       <c r="N18" s="36"/>
@@ -2579,17 +2611,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="33"/>
       <c r="D19" s="35" t="n">
         <v>150</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="35" t="n">
         <v>150</v>
@@ -2606,7 +2638,9 @@
       <c r="J19" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="K19" s="36"/>
+      <c r="K19" s="35" t="n">
+        <v>150</v>
+      </c>
       <c r="L19" s="36"/>
       <c r="M19" s="36"/>
       <c r="N19" s="36"/>
@@ -2678,17 +2712,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="33"/>
       <c r="D20" s="35" t="n">
         <v>55</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" s="35" t="n">
         <v>55</v>
@@ -2705,7 +2739,9 @@
       <c r="J20" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="K20" s="36"/>
+      <c r="K20" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="L20" s="36"/>
       <c r="M20" s="36"/>
       <c r="N20" s="36"/>
@@ -2777,17 +2813,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="39"/>
       <c r="D21" s="35" t="n">
         <v>72</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F21" s="35" t="n">
         <v>72</v>
@@ -2804,7 +2840,9 @@
       <c r="J21" s="35" t="n">
         <v>72</v>
       </c>
-      <c r="K21" s="36"/>
+      <c r="K21" s="35" t="n">
+        <v>72</v>
+      </c>
       <c r="L21" s="36"/>
       <c r="M21" s="36"/>
       <c r="N21" s="36"/>
@@ -2876,17 +2914,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="39"/>
       <c r="D22" s="35" t="n">
         <v>400</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" s="35" t="n">
         <v>400</v>
@@ -2903,7 +2941,9 @@
       <c r="J22" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="K22" s="36"/>
+      <c r="K22" s="35" t="n">
+        <v>400</v>
+      </c>
       <c r="L22" s="36"/>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -2975,34 +3015,36 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="33"/>
       <c r="D23" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E23" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="F23" s="35" t="s">
-        <v>55</v>
-      </c>
       <c r="G23" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I23" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="K23" s="35" t="s">
+        <v>56</v>
+      </c>
       <c r="L23" s="36"/>
       <c r="M23" s="36"/>
       <c r="N23" s="36"/>
@@ -3074,34 +3116,36 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="33"/>
       <c r="D24" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="35" t="s">
-        <v>59</v>
-      </c>
       <c r="G24" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I24" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="K24" s="36"/>
+        <v>60</v>
+      </c>
+      <c r="K24" s="35" t="s">
+        <v>60</v>
+      </c>
       <c r="L24" s="36"/>
       <c r="M24" s="36"/>
       <c r="N24" s="36"/>
@@ -3173,17 +3217,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F25" s="35" t="n">
         <v>1</v>
@@ -3200,7 +3244,9 @@
       <c r="J25" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="36"/>
+      <c r="K25" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L25" s="36"/>
       <c r="M25" s="36"/>
       <c r="N25" s="36"/>
@@ -3272,17 +3318,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F26" s="35" t="n">
         <v>1</v>
@@ -3299,7 +3345,9 @@
       <c r="J26" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="36"/>
+      <c r="K26" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L26" s="36"/>
       <c r="M26" s="36"/>
       <c r="N26" s="36"/>
@@ -3371,17 +3419,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="33"/>
       <c r="D27" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F27" s="35" t="n">
         <v>1</v>
@@ -3398,7 +3446,9 @@
       <c r="J27" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="36"/>
+      <c r="K27" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L27" s="36"/>
       <c r="M27" s="36"/>
       <c r="N27" s="36"/>
@@ -3470,17 +3520,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="33"/>
       <c r="D28" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F28" s="35" t="n">
         <v>1</v>
@@ -3497,7 +3547,9 @@
       <c r="J28" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="36"/>
+      <c r="K28" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L28" s="36"/>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
@@ -3569,34 +3621,36 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G29" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J29" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="K29" s="36"/>
+        <v>76</v>
+      </c>
+      <c r="K29" s="35" t="s">
+        <v>76</v>
+      </c>
       <c r="L29" s="36"/>
       <c r="M29" s="36"/>
       <c r="N29" s="36"/>
@@ -3668,10 +3722,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="35" t="n">
@@ -3681,21 +3735,23 @@
         <v>55</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="K30" s="36"/>
+        <v>79</v>
+      </c>
+      <c r="K30" s="35" t="s">
+        <v>79</v>
+      </c>
       <c r="L30" s="36"/>
       <c r="M30" s="36"/>
       <c r="N30" s="36"/>
@@ -3767,10 +3823,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="35" t="n">
@@ -3794,7 +3850,9 @@
       <c r="J31" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="K31" s="36"/>
+      <c r="K31" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="L31" s="36"/>
       <c r="M31" s="36"/>
       <c r="N31" s="36"/>
@@ -3866,34 +3924,36 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G32" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I32" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J32" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="K32" s="36"/>
+        <v>76</v>
+      </c>
+      <c r="K32" s="35" t="s">
+        <v>76</v>
+      </c>
       <c r="L32" s="36"/>
       <c r="M32" s="36"/>
       <c r="N32" s="36"/>
@@ -3965,34 +4025,36 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="39"/>
       <c r="D33" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E33" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I33" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="K33" s="36"/>
+        <v>86</v>
+      </c>
+      <c r="K33" s="35" t="s">
+        <v>86</v>
+      </c>
       <c r="L33" s="36"/>
       <c r="M33" s="36"/>
       <c r="N33" s="36"/>
@@ -4064,10 +4126,10 @@
     </row>
     <row r="34" s="42" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="41"/>
@@ -4077,6 +4139,7 @@
       <c r="H34" s="41"/>
       <c r="I34" s="41"/>
       <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
       <c r="V34" s="43"/>
       <c r="W34" s="44"/>
       <c r="AN34" s="43"/>
@@ -4088,34 +4151,36 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I35" s="34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J35" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="K35" s="45"/>
+        <v>92</v>
+      </c>
+      <c r="K35" s="34" t="s">
+        <v>92</v>
+      </c>
       <c r="L35" s="45"/>
       <c r="M35" s="45"/>
       <c r="N35" s="45"/>
@@ -4190,25 +4255,27 @@
         <v>2</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="34"/>
       <c r="E36" s="34"/>
       <c r="F36" s="34"/>
       <c r="G36" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H36" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I36" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J36" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="K36" s="36"/>
+        <v>94</v>
+      </c>
+      <c r="K36" s="34" t="s">
+        <v>95</v>
+      </c>
       <c r="L36" s="36"/>
       <c r="M36" s="36"/>
       <c r="N36" s="36"/>
@@ -4280,28 +4347,30 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="48" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
       <c r="G37" s="34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H37" s="34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I37" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J37" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="K37" s="36"/>
+        <v>95</v>
+      </c>
+      <c r="K37" s="34" t="s">
+        <v>100</v>
+      </c>
       <c r="L37" s="36"/>
       <c r="M37" s="36"/>
       <c r="N37" s="36"/>
@@ -4373,13 +4442,13 @@
     </row>
     <row r="38" s="42" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
@@ -4388,6 +4457,7 @@
       <c r="H38" s="41"/>
       <c r="I38" s="41"/>
       <c r="J38" s="41"/>
+      <c r="K38" s="41"/>
       <c r="V38" s="43"/>
       <c r="W38" s="44"/>
       <c r="AN38" s="43"/>
@@ -4399,16 +4469,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E39" s="34" t="n">
         <v>70</v>
@@ -4428,7 +4498,9 @@
       <c r="J39" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="K39" s="36"/>
+      <c r="K39" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="L39" s="36"/>
       <c r="M39" s="36"/>
       <c r="N39" s="36"/>
@@ -4500,16 +4572,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C40" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E40" s="34" t="n">
         <v>75</v>
@@ -4529,7 +4601,9 @@
       <c r="J40" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="K40" s="36"/>
+      <c r="K40" s="35" t="n">
+        <v>75</v>
+      </c>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
       <c r="N40" s="36"/>
@@ -4601,16 +4675,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C41" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E41" s="34" t="n">
         <v>60</v>
@@ -4630,7 +4704,9 @@
       <c r="J41" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="K41" s="36"/>
+      <c r="K41" s="35" t="n">
+        <v>60</v>
+      </c>
       <c r="L41" s="36"/>
       <c r="M41" s="36"/>
       <c r="N41" s="36"/>
@@ -4702,16 +4778,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C42" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E42" s="34" t="n">
         <v>90</v>
@@ -4731,7 +4807,9 @@
       <c r="J42" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="K42" s="36"/>
+      <c r="K42" s="35" t="n">
+        <v>90</v>
+      </c>
       <c r="L42" s="36"/>
       <c r="M42" s="36"/>
       <c r="N42" s="36"/>
@@ -4803,16 +4881,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C43" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E43" s="34" t="n">
         <v>1000</v>
@@ -4832,7 +4910,9 @@
       <c r="J43" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="K43" s="36"/>
+      <c r="K43" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="L43" s="36"/>
       <c r="M43" s="36"/>
       <c r="N43" s="36"/>
@@ -4904,16 +4984,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C44" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E44" s="34" t="n">
         <v>75</v>
@@ -4933,7 +5013,9 @@
       <c r="J44" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="K44" s="36"/>
+      <c r="K44" s="35" t="n">
+        <v>500</v>
+      </c>
       <c r="L44" s="36"/>
       <c r="M44" s="36"/>
       <c r="N44" s="36"/>
@@ -5005,16 +5087,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C45" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E45" s="34" t="n">
         <v>100</v>
@@ -5034,7 +5116,9 @@
       <c r="J45" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="K45" s="36"/>
+      <c r="K45" s="35" t="n">
+        <v>100</v>
+      </c>
       <c r="L45" s="36"/>
       <c r="M45" s="36"/>
       <c r="N45" s="36"/>
@@ -5106,16 +5190,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C46" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E46" s="34" t="n">
         <v>72</v>
@@ -5135,7 +5219,9 @@
       <c r="J46" s="35" t="n">
         <v>200</v>
       </c>
-      <c r="K46" s="36"/>
+      <c r="K46" s="35" t="n">
+        <v>200</v>
+      </c>
       <c r="L46" s="36"/>
       <c r="M46" s="36"/>
       <c r="N46" s="36"/>
@@ -5207,16 +5293,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C47" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E47" s="34" t="n">
         <v>65</v>
@@ -5236,7 +5322,9 @@
       <c r="J47" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="K47" s="36"/>
+      <c r="K47" s="35" t="n">
+        <v>120</v>
+      </c>
       <c r="L47" s="36"/>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
@@ -5308,16 +5396,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C48" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E48" s="34" t="n">
         <v>68</v>
@@ -5337,7 +5425,9 @@
       <c r="J48" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="K48" s="36"/>
+      <c r="K48" s="35" t="n">
+        <v>20</v>
+      </c>
       <c r="L48" s="36"/>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
@@ -5409,16 +5499,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C49" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E49" s="34" t="n">
         <v>72</v>
@@ -5438,7 +5528,9 @@
       <c r="J49" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="K49" s="36"/>
+      <c r="K49" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="L49" s="36"/>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
@@ -5510,16 +5602,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C50" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E50" s="34" t="n">
         <v>72</v>
@@ -5539,7 +5631,9 @@
       <c r="J50" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="K50" s="36"/>
+      <c r="K50" s="35" t="n">
+        <v>150</v>
+      </c>
       <c r="L50" s="36"/>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
@@ -5611,19 +5705,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C51" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F51" s="35" t="n">
         <v>55</v>
@@ -5640,7 +5734,9 @@
       <c r="J51" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="K51" s="36"/>
+      <c r="K51" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="L51" s="36"/>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
@@ -5712,19 +5808,19 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C52" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F52" s="35" t="n">
         <v>72</v>
@@ -5741,7 +5837,9 @@
       <c r="J52" s="35" t="n">
         <v>72</v>
       </c>
-      <c r="K52" s="36"/>
+      <c r="K52" s="35" t="n">
+        <v>72</v>
+      </c>
       <c r="L52" s="36"/>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
@@ -5813,19 +5911,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C53" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F53" s="35" t="n">
         <v>400</v>
@@ -5842,7 +5940,9 @@
       <c r="J53" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="K53" s="36"/>
+      <c r="K53" s="35" t="n">
+        <v>400</v>
+      </c>
       <c r="L53" s="36"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
@@ -5914,36 +6014,38 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C54" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G54" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H54" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I54" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J54" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="K54" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="K54" s="35" t="s">
+        <v>56</v>
+      </c>
       <c r="L54" s="36"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
@@ -6015,36 +6117,38 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C55" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E55" s="34" t="n">
         <v>72</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G55" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H55" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I55" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J55" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="K55" s="36"/>
+        <v>60</v>
+      </c>
+      <c r="K55" s="35" t="s">
+        <v>60</v>
+      </c>
       <c r="L55" s="36"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
@@ -6116,16 +6220,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C56" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E56" s="34" t="n">
         <v>720</v>
@@ -6145,7 +6249,9 @@
       <c r="J56" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K56" s="36"/>
+      <c r="K56" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L56" s="36"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
@@ -6217,16 +6323,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E57" s="34" t="n">
         <v>48</v>
@@ -6246,7 +6352,9 @@
       <c r="J57" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K57" s="36"/>
+      <c r="K57" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L57" s="36"/>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
@@ -6318,16 +6426,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C58" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>72</v>
@@ -6347,7 +6455,9 @@
       <c r="J58" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K58" s="36"/>
+      <c r="K58" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L58" s="36"/>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
@@ -6419,16 +6529,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C59" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E59" s="34" t="n">
         <v>84</v>
@@ -6448,7 +6558,9 @@
       <c r="J59" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K59" s="36"/>
+      <c r="K59" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="L59" s="36"/>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
@@ -6520,19 +6632,19 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C60" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F60" s="35" t="n">
         <v>55</v>
@@ -6549,7 +6661,9 @@
       <c r="J60" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="K60" s="36"/>
+      <c r="K60" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="L60" s="36"/>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
@@ -6621,19 +6735,19 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C61" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F61" s="35" t="n">
         <v>55</v>
@@ -6650,7 +6764,9 @@
       <c r="J61" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="K61" s="36"/>
+      <c r="K61" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="L61" s="36"/>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
@@ -6721,9 +6837,9 @@
       <c r="CA61" s="36"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K8:ZZ33 K39:ZZ61">
+  <conditionalFormatting sqref="L8:ZZ33 L39:ZZ61">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>#ref!&lt;&gt;K8</formula>
+      <formula>#ref!&lt;&gt;L8</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
+++ b/conformance_tests/foo/test_scripts/TestScript-foo.xlsx
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="132">
   <si>
     <t xml:space="preserve">Dummy Test</t>
   </si>
@@ -206,6 +206,9 @@
     <t xml:space="preserve">8</t>
   </si>
   <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -411,6 +414,9 @@
   </si>
   <si>
     <t xml:space="preserve">ts_u24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.04</t>
   </si>
   <si>
     <t xml:space="preserve">Y</t>
@@ -1324,7 +1330,9 @@
       <c r="K6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="19"/>
+      <c r="L6" s="18" t="s">
+        <v>4</v>
+      </c>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
       <c r="O6" s="19"/>
@@ -1429,7 +1437,9 @@
       <c r="K7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="26"/>
+      <c r="L7" s="25" t="s">
+        <v>13</v>
+      </c>
       <c r="M7" s="26"/>
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
@@ -1500,10 +1510,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="34" t="n">
@@ -1530,7 +1540,9 @@
       <c r="K8" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="L8" s="36"/>
+      <c r="L8" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="M8" s="36"/>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
@@ -1601,10 +1613,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="35" t="n">
@@ -1631,7 +1643,9 @@
       <c r="K9" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="35" t="n">
+        <v>75</v>
+      </c>
       <c r="M9" s="36"/>
       <c r="N9" s="36"/>
       <c r="O9" s="36"/>
@@ -1702,10 +1716,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="39"/>
       <c r="D10" s="35" t="n">
@@ -1732,7 +1746,9 @@
       <c r="K10" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="L10" s="36"/>
+      <c r="L10" s="35" t="n">
+        <v>60</v>
+      </c>
       <c r="M10" s="36"/>
       <c r="N10" s="36"/>
       <c r="O10" s="36"/>
@@ -1803,10 +1819,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="39"/>
       <c r="D11" s="35" t="n">
@@ -1833,7 +1849,9 @@
       <c r="K11" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="L11" s="36"/>
+      <c r="L11" s="35" t="n">
+        <v>90</v>
+      </c>
       <c r="M11" s="36"/>
       <c r="N11" s="36"/>
       <c r="O11" s="36"/>
@@ -1904,10 +1922,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="33"/>
       <c r="D12" s="35" t="n">
@@ -1934,7 +1952,9 @@
       <c r="K12" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" s="36"/>
+      <c r="L12" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="M12" s="36"/>
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
@@ -2005,17 +2025,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="35" t="n">
         <v>500</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="35" t="n">
         <v>500</v>
@@ -2035,7 +2055,9 @@
       <c r="K13" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="L13" s="36"/>
+      <c r="L13" s="35" t="n">
+        <v>500</v>
+      </c>
       <c r="M13" s="36"/>
       <c r="N13" s="36"/>
       <c r="O13" s="36"/>
@@ -2106,10 +2128,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="35" t="n">
@@ -2136,7 +2158,9 @@
       <c r="K14" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="L14" s="36"/>
+      <c r="L14" s="35" t="n">
+        <v>100</v>
+      </c>
       <c r="M14" s="36"/>
       <c r="N14" s="36"/>
       <c r="O14" s="36"/>
@@ -2207,17 +2231,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="35" t="n">
         <v>200</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" s="35" t="n">
         <v>200</v>
@@ -2237,7 +2261,9 @@
       <c r="K15" s="35" t="n">
         <v>200</v>
       </c>
-      <c r="L15" s="36"/>
+      <c r="L15" s="35" t="n">
+        <v>200</v>
+      </c>
       <c r="M15" s="36"/>
       <c r="N15" s="36"/>
       <c r="O15" s="36"/>
@@ -2308,17 +2334,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="35" t="n">
         <v>120</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="35" t="n">
         <v>120</v>
@@ -2338,7 +2364,9 @@
       <c r="K16" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="L16" s="36"/>
+      <c r="L16" s="35" t="n">
+        <v>120</v>
+      </c>
       <c r="M16" s="36"/>
       <c r="N16" s="36"/>
       <c r="O16" s="36"/>
@@ -2409,17 +2437,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="35" t="n">
         <v>20</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>20</v>
@@ -2439,7 +2467,9 @@
       <c r="K17" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="L17" s="36"/>
+      <c r="L17" s="35" t="n">
+        <v>20</v>
+      </c>
       <c r="M17" s="36"/>
       <c r="N17" s="36"/>
       <c r="O17" s="36"/>
@@ -2510,37 +2540,39 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="39"/>
       <c r="D18" s="35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E18" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="35" t="s">
-        <v>39</v>
-      </c>
       <c r="G18" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="L18" s="36"/>
+      <c r="L18" s="35" t="s">
+        <v>42</v>
+      </c>
       <c r="M18" s="36"/>
       <c r="N18" s="36"/>
       <c r="O18" s="36"/>
@@ -2611,17 +2643,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="33"/>
       <c r="D19" s="35" t="n">
         <v>150</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F19" s="35" t="n">
         <v>150</v>
@@ -2641,7 +2673,9 @@
       <c r="K19" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="L19" s="36"/>
+      <c r="L19" s="35" t="n">
+        <v>150</v>
+      </c>
       <c r="M19" s="36"/>
       <c r="N19" s="36"/>
       <c r="O19" s="36"/>
@@ -2712,17 +2746,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="33"/>
       <c r="D20" s="35" t="n">
         <v>55</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" s="35" t="n">
         <v>55</v>
@@ -2742,7 +2776,9 @@
       <c r="K20" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="L20" s="36"/>
+      <c r="L20" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="M20" s="36"/>
       <c r="N20" s="36"/>
       <c r="O20" s="36"/>
@@ -2813,17 +2849,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="39"/>
       <c r="D21" s="35" t="n">
         <v>72</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F21" s="35" t="n">
         <v>72</v>
@@ -2843,7 +2879,9 @@
       <c r="K21" s="35" t="n">
         <v>72</v>
       </c>
-      <c r="L21" s="36"/>
+      <c r="L21" s="35" t="n">
+        <v>72</v>
+      </c>
       <c r="M21" s="36"/>
       <c r="N21" s="36"/>
       <c r="O21" s="36"/>
@@ -2914,17 +2952,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="39"/>
       <c r="D22" s="35" t="n">
         <v>400</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22" s="35" t="n">
         <v>400</v>
@@ -2944,7 +2982,9 @@
       <c r="K22" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="L22" s="36"/>
+      <c r="L22" s="35" t="n">
+        <v>400</v>
+      </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
       <c r="O22" s="36"/>
@@ -3015,37 +3055,39 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="33"/>
       <c r="D23" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="35" t="s">
-        <v>56</v>
-      </c>
       <c r="G23" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I23" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K23" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="L23" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="L23" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="M23" s="36"/>
       <c r="N23" s="36"/>
       <c r="O23" s="36"/>
@@ -3116,37 +3158,39 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="33"/>
       <c r="D24" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E24" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="35" t="s">
-        <v>60</v>
-      </c>
       <c r="G24" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I24" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K24" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="L24" s="36"/>
+        <v>61</v>
+      </c>
+      <c r="L24" s="35" t="s">
+        <v>61</v>
+      </c>
       <c r="M24" s="36"/>
       <c r="N24" s="36"/>
       <c r="O24" s="36"/>
@@ -3217,17 +3261,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F25" s="35" t="n">
         <v>1</v>
@@ -3247,7 +3291,9 @@
       <c r="K25" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="36"/>
+      <c r="L25" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M25" s="36"/>
       <c r="N25" s="36"/>
       <c r="O25" s="36"/>
@@ -3318,17 +3364,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F26" s="35" t="n">
         <v>1</v>
@@ -3348,7 +3394,9 @@
       <c r="K26" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L26" s="36"/>
+      <c r="L26" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M26" s="36"/>
       <c r="N26" s="36"/>
       <c r="O26" s="36"/>
@@ -3419,17 +3467,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" s="33"/>
       <c r="D27" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F27" s="35" t="n">
         <v>1</v>
@@ -3449,7 +3497,9 @@
       <c r="K27" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L27" s="36"/>
+      <c r="L27" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M27" s="36"/>
       <c r="N27" s="36"/>
       <c r="O27" s="36"/>
@@ -3520,17 +3570,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="33"/>
       <c r="D28" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="35" t="n">
         <v>1</v>
@@ -3550,7 +3600,9 @@
       <c r="K28" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="36"/>
+      <c r="L28" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
       <c r="O28" s="36"/>
@@ -3621,37 +3673,39 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J29" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K29" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="L29" s="36"/>
+        <v>77</v>
+      </c>
+      <c r="L29" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="M29" s="36"/>
       <c r="N29" s="36"/>
       <c r="O29" s="36"/>
@@ -3722,10 +3776,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="35" t="n">
@@ -3735,24 +3789,26 @@
         <v>55</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K30" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="L30" s="36"/>
+        <v>80</v>
+      </c>
+      <c r="L30" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="M30" s="36"/>
       <c r="N30" s="36"/>
       <c r="O30" s="36"/>
@@ -3823,10 +3879,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="35" t="n">
@@ -3853,7 +3909,9 @@
       <c r="K31" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="L31" s="36"/>
+      <c r="L31" s="35" t="s">
+        <v>83</v>
+      </c>
       <c r="M31" s="36"/>
       <c r="N31" s="36"/>
       <c r="O31" s="36"/>
@@ -3924,37 +3982,39 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I32" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J32" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K32" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="L32" s="36"/>
+        <v>77</v>
+      </c>
+      <c r="L32" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="M32" s="36"/>
       <c r="N32" s="36"/>
       <c r="O32" s="36"/>
@@ -4025,37 +4085,39 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C33" s="39"/>
       <c r="D33" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E33" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I33" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K33" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="L33" s="36"/>
+        <v>88</v>
+      </c>
+      <c r="L33" s="35" t="s">
+        <v>88</v>
+      </c>
       <c r="M33" s="36"/>
       <c r="N33" s="36"/>
       <c r="O33" s="36"/>
@@ -4126,10 +4188,10 @@
     </row>
     <row r="34" s="42" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="41"/>
@@ -4140,6 +4202,7 @@
       <c r="I34" s="41"/>
       <c r="J34" s="41"/>
       <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
       <c r="V34" s="43"/>
       <c r="W34" s="44"/>
       <c r="AN34" s="43"/>
@@ -4151,37 +4214,39 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I35" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J35" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K35" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="L35" s="45"/>
+        <v>94</v>
+      </c>
+      <c r="L35" s="34" t="s">
+        <v>93</v>
+      </c>
       <c r="M35" s="45"/>
       <c r="N35" s="45"/>
       <c r="O35" s="45"/>
@@ -4255,28 +4320,28 @@
         <v>2</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="34"/>
       <c r="E36" s="34"/>
       <c r="F36" s="34"/>
       <c r="G36" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H36" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I36" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J36" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K36" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="L36" s="36"/>
+        <v>97</v>
+      </c>
+      <c r="L36" s="34"/>
       <c r="M36" s="36"/>
       <c r="N36" s="36"/>
       <c r="O36" s="36"/>
@@ -4347,31 +4412,31 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
       <c r="G37" s="34" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H37" s="34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I37" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J37" s="34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K37" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="L37" s="36"/>
+        <v>102</v>
+      </c>
+      <c r="L37" s="34"/>
       <c r="M37" s="36"/>
       <c r="N37" s="36"/>
       <c r="O37" s="36"/>
@@ -4442,13 +4507,13 @@
     </row>
     <row r="38" s="42" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
@@ -4458,6 +4523,7 @@
       <c r="I38" s="41"/>
       <c r="J38" s="41"/>
       <c r="K38" s="41"/>
+      <c r="L38" s="41"/>
       <c r="V38" s="43"/>
       <c r="W38" s="44"/>
       <c r="AN38" s="43"/>
@@ -4469,16 +4535,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C39" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E39" s="34" t="n">
         <v>70</v>
@@ -4501,7 +4567,9 @@
       <c r="K39" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="L39" s="36"/>
+      <c r="L39" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="M39" s="36"/>
       <c r="N39" s="36"/>
       <c r="O39" s="36"/>
@@ -4572,16 +4640,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C40" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E40" s="34" t="n">
         <v>75</v>
@@ -4604,7 +4672,9 @@
       <c r="K40" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="L40" s="36"/>
+      <c r="L40" s="35" t="n">
+        <v>75</v>
+      </c>
       <c r="M40" s="36"/>
       <c r="N40" s="36"/>
       <c r="O40" s="36"/>
@@ -4675,16 +4745,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C41" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E41" s="34" t="n">
         <v>60</v>
@@ -4707,7 +4777,9 @@
       <c r="K41" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="L41" s="36"/>
+      <c r="L41" s="35" t="n">
+        <v>60</v>
+      </c>
       <c r="M41" s="36"/>
       <c r="N41" s="36"/>
       <c r="O41" s="36"/>
@@ -4778,16 +4850,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C42" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E42" s="34" t="n">
         <v>90</v>
@@ -4810,7 +4882,9 @@
       <c r="K42" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="L42" s="36"/>
+      <c r="L42" s="35" t="n">
+        <v>90</v>
+      </c>
       <c r="M42" s="36"/>
       <c r="N42" s="36"/>
       <c r="O42" s="36"/>
@@ -4881,16 +4955,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C43" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E43" s="34" t="n">
         <v>1000</v>
@@ -4913,7 +4987,9 @@
       <c r="K43" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="L43" s="36"/>
+      <c r="L43" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="M43" s="36"/>
       <c r="N43" s="36"/>
       <c r="O43" s="36"/>
@@ -4984,16 +5060,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C44" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E44" s="34" t="n">
         <v>75</v>
@@ -5016,7 +5092,9 @@
       <c r="K44" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="L44" s="36"/>
+      <c r="L44" s="35" t="n">
+        <v>500</v>
+      </c>
       <c r="M44" s="36"/>
       <c r="N44" s="36"/>
       <c r="O44" s="36"/>
@@ -5087,16 +5165,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C45" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E45" s="34" t="n">
         <v>100</v>
@@ -5119,7 +5197,9 @@
       <c r="K45" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="L45" s="36"/>
+      <c r="L45" s="35" t="n">
+        <v>100</v>
+      </c>
       <c r="M45" s="36"/>
       <c r="N45" s="36"/>
       <c r="O45" s="36"/>
@@ -5190,16 +5270,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C46" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E46" s="34" t="n">
         <v>72</v>
@@ -5222,7 +5302,9 @@
       <c r="K46" s="35" t="n">
         <v>200</v>
       </c>
-      <c r="L46" s="36"/>
+      <c r="L46" s="35" t="n">
+        <v>200</v>
+      </c>
       <c r="M46" s="36"/>
       <c r="N46" s="36"/>
       <c r="O46" s="36"/>
@@ -5293,16 +5375,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C47" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E47" s="34" t="n">
         <v>65</v>
@@ -5325,7 +5407,9 @@
       <c r="K47" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="L47" s="36"/>
+      <c r="L47" s="35" t="n">
+        <v>120</v>
+      </c>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
       <c r="O47" s="36"/>
@@ -5396,16 +5480,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C48" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E48" s="34" t="n">
         <v>68</v>
@@ -5428,7 +5512,9 @@
       <c r="K48" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="L48" s="36"/>
+      <c r="L48" s="35" t="n">
+        <v>20</v>
+      </c>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
       <c r="O48" s="36"/>
@@ -5499,16 +5585,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C49" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E49" s="34" t="n">
         <v>72</v>
@@ -5531,7 +5617,9 @@
       <c r="K49" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="L49" s="36"/>
+      <c r="L49" s="35" t="n">
+        <v>70</v>
+      </c>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
       <c r="O49" s="36"/>
@@ -5602,16 +5690,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C50" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E50" s="34" t="n">
         <v>72</v>
@@ -5634,7 +5722,9 @@
       <c r="K50" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="L50" s="36"/>
+      <c r="L50" s="35" t="n">
+        <v>150</v>
+      </c>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
       <c r="O50" s="36"/>
@@ -5705,19 +5795,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C51" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F51" s="35" t="n">
         <v>55</v>
@@ -5737,7 +5827,9 @@
       <c r="K51" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="L51" s="36"/>
+      <c r="L51" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
       <c r="O51" s="36"/>
@@ -5808,19 +5900,19 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C52" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F52" s="35" t="n">
         <v>72</v>
@@ -5840,7 +5932,9 @@
       <c r="K52" s="35" t="n">
         <v>72</v>
       </c>
-      <c r="L52" s="36"/>
+      <c r="L52" s="35" t="n">
+        <v>72</v>
+      </c>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
       <c r="O52" s="36"/>
@@ -5911,19 +6005,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C53" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F53" s="35" t="n">
         <v>400</v>
@@ -5943,7 +6037,9 @@
       <c r="K53" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="L53" s="36"/>
+      <c r="L53" s="35" t="n">
+        <v>400</v>
+      </c>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
       <c r="O53" s="36"/>
@@ -6014,39 +6110,41 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C54" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G54" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H54" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I54" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J54" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K54" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="L54" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="L54" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
       <c r="O54" s="36"/>
@@ -6117,39 +6215,41 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C55" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E55" s="34" t="n">
         <v>72</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G55" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H55" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I55" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J55" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K55" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="L55" s="36"/>
+        <v>61</v>
+      </c>
+      <c r="L55" s="35" t="s">
+        <v>61</v>
+      </c>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="36"/>
@@ -6220,16 +6320,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C56" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E56" s="34" t="n">
         <v>720</v>
@@ -6252,7 +6352,9 @@
       <c r="K56" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L56" s="36"/>
+      <c r="L56" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
       <c r="O56" s="36"/>
@@ -6323,16 +6425,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C57" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E57" s="34" t="n">
         <v>48</v>
@@ -6355,7 +6457,9 @@
       <c r="K57" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L57" s="36"/>
+      <c r="L57" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
       <c r="O57" s="36"/>
@@ -6426,16 +6530,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C58" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>72</v>
@@ -6458,7 +6562,9 @@
       <c r="K58" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L58" s="36"/>
+      <c r="L58" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
       <c r="O58" s="36"/>
@@ -6529,16 +6635,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C59" s="39" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E59" s="34" t="n">
         <v>84</v>
@@ -6561,7 +6667,9 @@
       <c r="K59" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L59" s="36"/>
+      <c r="L59" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
       <c r="O59" s="36"/>
@@ -6632,19 +6740,19 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C60" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F60" s="35" t="n">
         <v>55</v>
@@ -6664,7 +6772,9 @@
       <c r="K60" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="L60" s="36"/>
+      <c r="L60" s="35" t="n">
+        <v>55</v>
+      </c>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -6735,19 +6845,19 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C61" s="33" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F61" s="35" t="n">
         <v>55</v>
@@ -6767,7 +6877,9 @@
       <c r="K61" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="L61" s="36"/>
+      <c r="L61" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36"/>
@@ -6837,9 +6949,9 @@
       <c r="CA61" s="36"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L8:ZZ33 L39:ZZ61">
+  <conditionalFormatting sqref="M8:ZZ33 M39:ZZ61">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>#ref!&lt;&gt;L8</formula>
+      <formula>#ref!&lt;&gt;M8</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
